--- a/docs/Backlog_N2.xlsx
+++ b/docs/Backlog_N2.xlsx
@@ -669,7 +669,7 @@
           <t>• Templates de issue (task, bug, ux) e de PR no main
 • CODEOWNERS e ruleset do main ativos
 • Workflows Delivery rules e Completion guard rodando
-• Workflows do Project configurados
+• Workflows do Project configurados: Item added to project → To do, Item reopened → In progress, Code changes requested → In progress
 • Equipe avisada do fluxo
 • Evidência (link, print ou vídeo) anexada na issue</t>
         </is>
@@ -716,7 +716,7 @@
       </c>
       <c r="I6" s="5" t="inlineStr">
         <is>
-          <t>Em andamento</t>
+          <t>Concluída</t>
         </is>
       </c>
       <c r="J6" s="5" t="inlineStr">
@@ -733,7 +733,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="82" customHeight="1">
+    <row r="7" ht="160" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
           <t>#31</t>
@@ -784,16 +784,22 @@
       </c>
       <c r="K7" s="5" t="inlineStr">
         <is>
-          <t>• Express + TypeScript em `apps/api`, em camadas: rota → controle → serviço → repositório → model
-• Erro e paginação no mesmo formato que o front já espera em `apps/web/src/lib/repositories`
-• `GET /health`
-• Lint, tipos e testes (supertest) rodando no CI
-• Teste automatizado do caso principal
+          <t>• Express + TypeScript em `apps/api`, em camadas: rota → controle → serviço → repositório → model, uma pasta por camada
+• `apps/api` é um workspace (`@correctio/api`) e `npm run lint`, `npm run typecheck`, `npm test` e `npm run build` da raiz rodam front e API
+• `GET /health` responde 200 sem login, passando por rota, controle e serviço
+• Erro no formato `{ code, message }` com os códigos do `StorageError` (`not-found`, `invalid`, `conflict`, `failure`), mais `unauthorized` (401) e `too-many-requests` (429); erro desconhecido sem stack trace
+• Paginação no mesmo formato que o front já espera em `apps/web/src/lib/repositories`: `{ items, total }`, `page` e `pageSize` com padrão 1 e 50, `pageSize` acima do teto responde 400
+• `requireAuth` fechado por padrão: rota protegida sem token responde 401
+• A API valida com os schemas Zod do front, sem cópia
+• CORS só para as origens de `CORS_ORIGINS`; `helmet` e limite de 100 KB no JSON
+• Lint com as mesmas regras de comentário do front, tipos e testes (supertest) rodando no CI
+• `apps/api/README.md` explica como rodar localmente e as convenções da API, incluindo onde divergem da Spec
+• Testes automatizados do caso principal: health, rota inexistente, 401 sem token, formato de erro, paginação e CORS
 • Vídeo do teste anexado no PR</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="69" customHeight="1">
+    <row r="8" ht="95" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
           <t>#36</t>
@@ -844,15 +850,17 @@
       </c>
       <c r="K8" s="5" t="inlineStr">
         <is>
-          <t>• vitest e @vitest/coverage-v8 na 5.x (corrige tinypool e @vitest/mocker)
-• npm audit fix para brace-expansion e source-map-js
-• npm audit --audit-level=high passa
-• Lint, tipos, testes e build verde na main
+          <t>• `vitest` e `@vitest/coverage-v8` na 5.x, na mesma versão (corrige `tinypool` e `@vitest/mocker`)
+• `npm audit fix` para `brace-expansion` e `source-map-js` (e `joi`, que sai junto)
+• `npm audit --audit-level=high` passa, sem vulnerabilidade alta nem crítica
+• Cobertura continua em 80% ou mais com as mesmas exclusões, e o percentual antes e depois está na descrição do PR
+• Lint, tipos, testes, build e Cypress verdes no PR, que é o mesmo portão que roda para a `main`
+• Versão do Vitest atualizada na seção 7 do `readme.md`
 • Evidência (link, print ou vídeo) anexada na issue</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="82" customHeight="1">
+    <row r="9" ht="147" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
           <t>#32</t>
@@ -903,16 +911,21 @@
       </c>
       <c r="K9" s="5" t="inlineStr">
         <is>
-          <t>• MySQL hospedado, acessível pela API, com as credenciais só nos secrets do repositório
-• Migrations de todas as entidades do `docs/Modelo_de_Dados.md`, sem renomear chaves da Spec
-• Soft delete e auditoria
-• `.env.example` documentado
-• Teste automatizado do caso principal
+          <t>• MySQL hospedado, acessível pela API, com as credenciais só nos secrets do repositório e nas variáveis do host
+• Migrations de todas as entidades do `docs/Modelo_de_Dados.md`, sem renomear chaves da Spec, incluindo `class_enrollments`, `exam_assignments`, `refresh_tokens`, `students.userId`, `classes.inviteCode`, `clientCorrectionId` e `syncStatus`
+• Colunas com o nome exato do campo do contrato e enums com os valores exatos
+• Soft delete: cada entidade arquiva pelo próprio campo (`deletedAt` ou `status`) e nenhuma chave estrangeira apaga em cascata
+• Auditoria: `createdAt`/`updatedAt` nas tabelas e tabela `activity_logs` (log geral), sem conteúdo de dado pessoal
+• Acréscimos do grupo registrados em `docs/Modelo_de_Dados.md`, marcados com `+`: `Student.removedAt`, `Question.createdAt` e a entidade `ActivityLog`
+• `.env.example` documentado e MySQL local descrito no `apps/api/README.md`
+• Migrations aplicam, desfazem e reaplicam num banco vazio
+• `GET /health` responde 503 quando o banco está fora
+• Testes automatizados do caso principal, incluindo o que confere as colunas contra o contrato
 • Vídeo do teste anexado no PR</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="69" customHeight="1">
+    <row r="10" ht="134" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
           <t>#38</t>
@@ -963,249 +976,272 @@
       </c>
       <c r="K10" s="5" t="inlineStr">
         <is>
-          <t>• Implementa a interface de lib/repositories sem mudar telas
-• Token, erros e paginação
-• URL da API por variável de ambiente
+          <t>• Implementa a interface de `lib/repositories` sem mudar telas: repositório HTTP genérico cumpre o `OwnedRepository` de `types.ts`
+• Token enviado como `Authorization: Bearer`, vindo de uma função injetada; 401 chama `onUnauthorized`
+• Erros convertidos em `StorageError` com o `code` e a mensagem do servidor; 404 no `getById` devolve `null`
+• Paginação: `ListParams` vira query string e `{ items, total }` vira `Page&lt;T&gt;`
+• URL da API por variável de ambiente (`VITE_API_URL`), tipada e documentada em `apps/web/.env.example`
+• Resposta validada pelos schemas de `lib/schemas`, sem descartar campo desconhecido
+• `update` envia só os campos recebidos e nenhum pedido envia `teacherId`
+• A fábrica continua devolvendo os repositórios locais: o site publicado não muda com esta tarefa
+• Testes automatizados do caso principal, com `fetch` simulado: query string, cabeçalho de token, cada linha da tabela de erros, `null` no 404 e campo desconhecido preservado
+• Vídeo do teste anexado no PR</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="69" customHeight="1">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>#83</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>po: settle the open decisions with the professor (Firebase Auth, A/B/C versions)</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Validação de escopo</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>Processo e escopo</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="inlineStr">
+        <is>
+          <t>Heloísa Fogaça</t>
+        </is>
+      </c>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>heloisaFogaca</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>46307</v>
+      </c>
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>A fazer</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>Pendência do README (professora)</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="inlineStr">
+        <is>
+          <t>• Firebase Auth no lugar dos endpoints `/auth` da Spec: decisão registrada, antes da #40 começar
+• Versionamento A/B/C de questões (provas realmente diferentes por aluno): entra ou não no escopo
+• Respostas registradas no README e em `docs/` (requisitos, arquitetura e, se mudar, segurança)
+• Decisão comentada na #40, na #45 e na #84
+• Evidência (link, print ou vídeo) anexada na issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="95" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>#26</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>diagrama de caso de uso</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Documentação</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>Documentação</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="inlineStr">
+        <is>
+          <t>Heloísa Fogaça</t>
+        </is>
+      </c>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>heloisaFogaca</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>46308</v>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>#36</t>
+        </is>
+      </c>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>Em andamento</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>Issue já existente</t>
+        </is>
+      </c>
+      <c r="K12" s="5" t="inlineStr">
+        <is>
+          <t>• PR #30 atualizado com a `main`, depois da correção do `npm audit` lá (#36)
+• `docs/uml/use_case_diagram/01_Diagrama_de_Caso_de_Uso.md` renomeado para inglês (ex.: `docs/uml/use-case-diagram.md`), com as imagens aparecendo no GitHub
+• Prints do passo a passo da construção (uma imagem por etapa) no PR, em `docs/uml/`
+• Corpo do PR #30 com o template, `Closes #26` e label `docs`
+• Título do PR no formato `docs: ...`
+• Check *Lint, tipos, testes e build* verde no PR #30
+• Evidência (link, print ou vídeo) anexada na issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="160" customHeight="1">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>#39</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>ci: run API tests and migrations, deploy the API</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Infraestrutura</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>Infraestrutura e API</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>Priscila Torres</t>
+        </is>
+      </c>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>PrieTorres</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>46308</v>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>#31, #32</t>
+        </is>
+      </c>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>A fazer</t>
+        </is>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>Plano da N2</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="inlineStr">
+        <is>
+          <t>• Testes da API em todo PR, com MySQL de teste no CI
+• Migrations aplicadas num banco vazio em todo PR, antes dos testes
+• `checks.yml`, `release.yml` e o job `sonar` continuam verdes com os testes que usam banco
+• SonarCloud analisa `apps/api/src` e recebe a cobertura da API
+• Job Cypress sobe API e MySQL e builda o front apontando para eles
+• Migrations aplicadas no deploy, antes da versão nova entrar no ar
+• API publicada com URL fixa, em HTTPS, e `GET /health` conferido ao fim de cada deploy
+• CORS da API publicada aceita `https://prietorres.github.io` e recusa outras origens
+• `deploy.yml` builda o front com `VITE_API_URL` vindo da variável do repositório
+• `docs/CI_CD.md` atualizado com os novos passos, *secrets* e variáveis
+• Credenciais do provedor de e-mail, usado pela recuperação de senha da #40, guardadas como *secret* e passadas à API publicada, nunca no código
+• Evidência (link, print ou vídeo) anexada na issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="160" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>#40</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>feat: authentication end to end (register, sign-in, refresh, sign-out)</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Desenvolvimento</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>Acesso e consulta pública</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="inlineStr">
+        <is>
+          <t>Heloísa Fogaça</t>
+        </is>
+      </c>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>heloisaFogaca</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>46308</v>
+      </c>
+      <c r="H14" s="5" t="inlineStr">
+        <is>
+          <t>#31, #32, #38, #83</t>
+        </is>
+      </c>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>A fazer</t>
+        </is>
+      </c>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>Plano da N2</t>
+        </is>
+      </c>
+      <c r="K14" s="5" t="inlineStr">
+        <is>
+          <t>• Senha gravada só como hash (bcrypt ou argon2) em `passwordHash`, que nunca sai na resposta da API
+• Rate limit no login: bloqueio após 5 falhas em 15 minutos, com 429 e `Retry-After`, e a tela de login avisa
+• Cadastro exige senha de no mínimo 8 caracteres, no front e na API, e recusa e-mail já cadastrado
+• RefreshToken persistido só como `tokenHash`, renovado a cada refresh e revogável: `logout` revoga o do dispositivo, `logout-all` revoga todos
+• Telas de login, cadastro e recuperação de senha usam a API
+• Rotas privadas redirecionam para `/entrar` sem sessão
+• Sair limpa o cache, e outro professor no mesmo navegador não vê dado do anterior
+• E-mail de recuperação de senha enviado de verdade, com a mesma resposta para e-mail com e sem conta
+• O link do e-mail abre a etapa de nova senha, vale uma vez só e expira
+• Testes com supertest para cadastro, e-mail duplicado, login certo e errado, bloqueio, refresh, logout, logout de todos e recuperação com e sem conta
 • Testes automatizados do caso principal
 • Vídeo do teste anexado no PR</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="56" customHeight="1">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>#83</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>po: settle the open decisions with the professor (Firebase Auth, A/B/C versions)</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>Validação de escopo</t>
-        </is>
-      </c>
-      <c r="D11" s="5" t="inlineStr">
-        <is>
-          <t>Processo e escopo</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>Heloísa Fogaça</t>
-        </is>
-      </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>heloisaFogaca</t>
-        </is>
-      </c>
-      <c r="G11" s="6" t="n">
-        <v>46307</v>
-      </c>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I11" s="5" t="inlineStr">
-        <is>
-          <t>A fazer</t>
-        </is>
-      </c>
-      <c r="J11" s="5" t="inlineStr">
-        <is>
-          <t>Pendência do README (professora)</t>
-        </is>
-      </c>
-      <c r="K11" s="5" t="inlineStr">
-        <is>
-          <t>• Firebase Auth no lugar dos endpoints `/auth` da Spec: decisão registrada, antes da #40 começar
-• Versionamento A/B/C de questões (provas realmente diferentes por aluno): entra ou não no escopo
-• Respostas registradas no README e em `docs/`
-• Evidência (link, print ou vídeo) anexada na issue</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="43" customHeight="1">
-      <c r="A12" s="4" t="inlineStr">
-        <is>
-          <t>#26</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>diagrama de caso de uso</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>Documentação</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="inlineStr">
-        <is>
-          <t>Documentação</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>Heloísa Fogaça</t>
-        </is>
-      </c>
-      <c r="F12" s="5" t="inlineStr">
-        <is>
-          <t>heloisaFogaca</t>
-        </is>
-      </c>
-      <c r="G12" s="6" t="n">
-        <v>46308</v>
-      </c>
-      <c r="H12" s="5" t="inlineStr">
-        <is>
-          <t>#36</t>
-        </is>
-      </c>
-      <c r="I12" s="5" t="inlineStr">
-        <is>
-          <t>Em andamento</t>
-        </is>
-      </c>
-      <c r="J12" s="5" t="inlineStr">
-        <is>
-          <t>Issue já existente</t>
-        </is>
-      </c>
-      <c r="K12" s="5" t="inlineStr">
-        <is>
-          <t>• PR #30 atualizado com a `main`, depois da correção do `npm audit` lá (#36)
-• `docs/uml/01_Diagrama_de_Caso_de_Uso.md` renomeado para inglês (ex.: `docs/uml/use-case-diagram.md`)
-• Corpo do PR #30 com o template, `Closes #26` e label `docs`</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="56" customHeight="1">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>#39</t>
-        </is>
-      </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>ci: run API tests and migrations, deploy the API</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>Infraestrutura</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>Infraestrutura e API</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="inlineStr">
-        <is>
-          <t>Priscila Torres</t>
-        </is>
-      </c>
-      <c r="F13" s="5" t="inlineStr">
-        <is>
-          <t>PrieTorres</t>
-        </is>
-      </c>
-      <c r="G13" s="6" t="n">
-        <v>46308</v>
-      </c>
-      <c r="H13" s="5" t="inlineStr">
-        <is>
-          <t>#32</t>
-        </is>
-      </c>
-      <c r="I13" s="5" t="inlineStr">
-        <is>
-          <t>A fazer</t>
-        </is>
-      </c>
-      <c r="J13" s="5" t="inlineStr">
-        <is>
-          <t>Plano da N2</t>
-        </is>
-      </c>
-      <c r="K13" s="5" t="inlineStr">
-        <is>
-          <t>• Testes da API em todo PR
-• Migrations aplicadas no deploy
-• API publicada com URL fixa
-• Evidência (link, print ou vídeo) anexada na issue</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="95" customHeight="1">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>#40</t>
-        </is>
-      </c>
-      <c r="B14" s="5" t="inlineStr">
-        <is>
-          <t>feat: authentication end to end (register, sign-in, refresh, sign-out)</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="inlineStr">
-        <is>
-          <t>Desenvolvimento</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="inlineStr">
-        <is>
-          <t>Acesso e consulta pública</t>
-        </is>
-      </c>
-      <c r="E14" s="5" t="inlineStr">
-        <is>
-          <t>Heloísa Fogaça</t>
-        </is>
-      </c>
-      <c r="F14" s="5" t="inlineStr">
-        <is>
-          <t>heloisaFogaca</t>
-        </is>
-      </c>
-      <c r="G14" s="6" t="n">
-        <v>46308</v>
-      </c>
-      <c r="H14" s="5" t="inlineStr">
-        <is>
-          <t>#32, HTTP adapter</t>
-        </is>
-      </c>
-      <c r="I14" s="5" t="inlineStr">
-        <is>
-          <t>A fazer</t>
-        </is>
-      </c>
-      <c r="J14" s="5" t="inlineStr">
-        <is>
-          <t>Plano da N2</t>
-        </is>
-      </c>
-      <c r="K14" s="5" t="inlineStr">
-        <is>
-          <t>• Senha com hash e rate limit no login
-• RefreshToken persistido e revogável
-• Telas de acesso usam a API
-• Rotas privadas redirecionam sem sessão
-• Testes automatizados do caso principal
-• Vídeo do teste anexado no PR
-• E-mail de recuperação de senha enviado de verdade, sem revelar se o e-mail tem conta</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="69" customHeight="1">
+    <row r="15" ht="82" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
         <is>
           <t>#53</t>
@@ -1256,15 +1292,16 @@
       </c>
       <c r="K15" s="5" t="inlineStr">
         <is>
-          <t>• Usar as telas (login, cadastro, recuperar senha, consulta por QR, privacidade) na versão publicada como professor faria
+          <t>• Usar as telas (login, cadastro, recuperar senha, consulta por QR, privacidade) na versão publicada como professor faria, e a consulta por QR como o aluno, no celular
+• Navegação só por teclado e largura de 360 px conferidas nas cinco telas
 • Abrir uma issue UX suggestion por melhoria, com print
-• Priorizar as sugestões por impacto
+• Priorizar as sugestões por impacto, com a lista ordenada em comentário nesta issue
 • Registrar a sessão de uso no diário
 • Evidência (link, print ou vídeo) anexada na issue</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="69" customHeight="1">
+    <row r="16" ht="95" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
           <t>#57</t>
@@ -1316,14 +1353,16 @@
       <c r="K16" s="5" t="inlineStr">
         <is>
           <t>• Usar as telas (turmas, alunos, importação, aplicações, PDF) na versão publicada como professor faria
+• Testar em 360 px de largura e só com o teclado
+• Conferir P3, P5, P11, P12, P13 e P14 contra a seção 8.4 da especificação
 • Abrir uma issue UX suggestion por melhoria, com print
-• Priorizar as sugestões por impacto
+• Priorizar as sugestões por impacto, com a lista ordenada num comentário desta issue
 • Registrar a sessão de uso no diário
 • Evidência (link, print ou vídeo) anexada na issue</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="69" customHeight="1">
+    <row r="17" ht="95" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
           <t>#61</t>
@@ -1359,7 +1398,7 @@
       </c>
       <c r="H17" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>— (revisa a versão publicada da N1, que já existe)</t>
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr">
@@ -1375,8 +1414,10 @@
       <c r="K17" s="5" t="inlineStr">
         <is>
           <t>• Usar as telas (banco de questões, provas, geração automática) na versão publicada como professor faria
+• Conferir as telas P6, P7, P8, P9, P9b e P10 contra a especificação da seção 8.4
+• Repetir o uso em 360 px e só com teclado
 • Abrir uma issue UX suggestion por melhoria, com print
-• Priorizar as sugestões por impacto
+• Priorizar as sugestões por impacto, em comentário nesta issue com o link de cada uma
 • Registrar a sessão de uso no diário
 • Evidência (link, print ou vídeo) anexada na issue</t>
         </is>
@@ -1433,15 +1474,15 @@
       </c>
       <c r="K18" s="5" t="inlineStr">
         <is>
-          <t>• Usar as telas (correção, revisão, pendentes, painel, relatórios, perfil) na versão publicada como professor faria
+          <t>• Usar as telas (correção, revisão, pendentes, painel, relatórios, perfil) na versão publicada como professor faria, no celular e no computador
 • Abrir uma issue UX suggestion por melhoria, com print
-• Priorizar as sugestões por impacto
+• Priorizar as sugestões por impacto, com o campo "Impacto" preenchido e a lista ordenada nesta issue
 • Registrar a sessão de uso no diário
 • Evidência (link, print ou vídeo) anexada na issue</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="69" customHeight="1">
+    <row r="19" ht="147" customHeight="1">
       <c r="A19" s="4" t="inlineStr">
         <is>
           <t>#41</t>
@@ -1449,7 +1490,7 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>feat(api): classes, students and enrollments CRUD</t>
+          <t>feat(api): classes and students CRUD</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
@@ -1477,7 +1518,7 @@
       </c>
       <c r="H19" s="5" t="inlineStr">
         <is>
-          <t>Auth</t>
+          <t>#31, #32, #40</t>
         </is>
       </c>
       <c r="I19" s="5" t="inlineStr">
@@ -1492,15 +1533,21 @@
       </c>
       <c r="K19" s="5" t="inlineStr">
         <is>
-          <t>• Criar/listar/editar/excluir (soft delete)
-• Dados isolados por professor dono
-• Atualização é mesclagem
-• Testes automatizados do caso principal
-• Vídeo do teste anexado no PR</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="69" customHeight="1">
+          <t>• Criar/listar/editar/excluir (soft delete) turmas: as 6 rotas de turma respondem, e todas exigem login
+• Rotas de aluno respondem e exigem login: listar por turma, cadastrar, importar em lote, editar, remover e anonimizar
+• Excluir não apaga nada do banco: arquivar turma muda `status` para `"archived"`, restaurar volta para `"active"`, e remover aluno preenche `removedAt` e mantém a linha (RF09)
+• Dados isolados por professor dono: turma ou aluno de outro professor responde 404 em todas as rotas, inclusive remover e anonimizar (teste com dois professores)
+• Atualização é mesclagem: o PATCH não apaga campo que não foi enviado (`inviteCode`, `status`, `userId`)
+• Turma repetida (mesmo nome e período, sem diferenciar acento e caixa) e matrícula repetida na mesma turma respondem 409
+• `inviteCode` é gerado pelo servidor na criação e é único
+• A importação grava as linhas novas e responde quantas entraram e quantas foram ignoradas
+• Anonimizar apaga nome, matrícula e e-mail e mantém o registro (RF38)
+• Testes automatizados do caso principal: supertest para criar, listar com busca, editar, arquivar, restaurar, cadastrar, importar, remover e anonimizar aluno, e acesso de outro professor
+• Vídeo do teste anexado no PR (chamando as rotas pelo Postman ou Insomnia, ou rodando os testes)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="82" customHeight="1">
       <c r="A20" s="4" t="inlineStr">
         <is>
           <t>#70</t>
@@ -1551,15 +1598,16 @@
       </c>
       <c r="K20" s="5" t="inlineStr">
         <is>
-          <t>• DER gerado a partir das migrations
-• Imagem em docs/ e no README
-• Evidência (link, print ou vídeo) anexada na issue
-• Imagem do DER em `docs/modelo-dados/`
-• Dicionário de dados: uma tabela por entidade, com campo, tipo e descrição</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="82" customHeight="1">
+          <t>• DER gerado a partir das migrations (#32)
+• Imagem do DER em `docs/data-model/` (a pasta `docs/modelo-dados/` do modelo da disciplina, com nome em inglês)
+• Imagem em `docs/` e exibida no README
+• Todas as tabelas das migrations aparecem, inclusive as reservadas para escopo futuro
+• Dicionário de dados: uma tabela por entidade, com campo, tipo e descrição
+• Evidência (link, print ou vídeo) anexada na issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="108" customHeight="1">
       <c r="A21" s="4" t="inlineStr">
         <is>
           <t>#77</t>
@@ -1614,12 +1662,14 @@
 • Com mais de uma aplicação gerada, o professor escolhe a aplicação antes de enviar
 • Sem aplicação gerada, a tela explica o que fazer
 • O tour do painel continua apontando para o botão certo
-• Cenário no Cypress do painel até a tela de correção
+• A P1 em `docs/Correctio_Requisitos_e_Telas.md` descreve o caminho novo
+• Cenário no Cypress do painel até a tela de correção, com uma, várias e nenhuma aplicação gerada
+• Testes automatizados do caso principal
 • Vídeo do teste anexado no PR</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="69" customHeight="1">
+    <row r="22" ht="134" customHeight="1">
       <c r="A22" s="4" t="inlineStr">
         <is>
           <t>#42</t>
@@ -1655,7 +1705,7 @@
       </c>
       <c r="H22" s="5" t="inlineStr">
         <is>
-          <t>Classes API</t>
+          <t>#41, #38</t>
         </is>
       </c>
       <c r="I22" s="5" t="inlineStr">
@@ -1670,385 +1720,421 @@
       </c>
       <c r="K22" s="5" t="inlineStr">
         <is>
-          <t>• Lista, criar/editar e detalhe da turma usam a API
+          <t>• Lista, criar/editar e detalhe da turma usam a API (P3, modal da P4 e P5)
+• Cadastrar, remover e anonimizar aluno usam a API
 • Importação em lote grava no banco
-• Erros da API aparecem na tela
+• Depois de importar, a tela mostra quantos alunos entraram e quantos foram ignorados
+• A prévia da importação aponta e-mail malformado antes de enviar
+• O aviso de privacidade aparece também na importação (RF39)
+• Erros da API aparecem na tela: ao salvar turma, cadastrar aluno, arquivar e restaurar turma, remover e anonimizar aluno, e ao carregar os alunos
+• `ImportStudentsDialog` usa um hook e não chama `useServices` direto
+• Testes automatizados do caso principal: hook de importação, regra do e-mail em `parseStudents`, e Cypress de importação, remoção e erro em `classes.cy.ts`
+• Vídeo do teste anexado no PR</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="121" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>#43</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>feat(api): question bank CRUD with server-side filters</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Desenvolvimento</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>Questões e provas</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="inlineStr">
+        <is>
+          <t>Cleberson Maia</t>
+        </is>
+      </c>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>maia202</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>46310</v>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>#31, #32, #40</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>A fazer</t>
+        </is>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>Plano da N2</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="inlineStr">
+        <is>
+          <t>• As 7 rotas respondem, e todas exigem login
+• Um professor não vê nem altera questão de outro (teste com dois professores)
+• A validação recusa o mesmo que o formulário recusa
+• Excluir só preenche `deletedAt`, e restaurar desfaz. Nada é apagado do banco.
+• Filtros, ordenação e paginação acontecem no servidor
+• O PATCH mescla e não apaga campo que não foi enviado; `null` remove o valor
+• `GET /questions/:id` devolve também questão excluída
+• Testes com supertest para criar, listar com filtro, editar, excluir, restaurar e acesso de outro professor
+• Vídeo do teste anexado no PR (chamando as rotas pelo Postman ou Insomnia, ou rodando os testes)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="121" customHeight="1">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>#44</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>feat(web): question bank screens on the API</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>Desenvolvimento</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>Questões e provas</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>Cleberson Maia</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>maia202</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>46311</v>
+      </c>
+      <c r="H24" s="5" t="inlineStr">
+        <is>
+          <t>#43, #38</t>
+        </is>
+      </c>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t>A fazer</t>
+        </is>
+      </c>
+      <c r="J24" s="5" t="inlineStr">
+        <is>
+          <t>Plano da N2</t>
+        </is>
+      </c>
+      <c r="K24" s="5" t="inlineStr">
+        <is>
+          <t>• Lista (P6) e criar/editar (P7) usam a API: criar, editar, duplicar, excluir e restaurar gravam no banco e continuam lá depois de recarregar a página
+• Filtros de tipo, tags, "Sem tag", busca e ordenação chamam o servidor (`GET /questions`), sem filtrar a página no navegador
+• Tags do filtro e das sugestões do formulário vêm de `GET /questions/tags`, sem listar 1000 questões
+• A lista mostra o total e deixa ver as questões além da primeira página
+• Editar uma objetiva para discursiva não deixa `alternatives` nem `correctAlternativeId` para trás no banco
+• Questão inexistente ou de outro professor mostra "não encontrada", e não um formulário vazio
+• Teste unitário do repositório filtrando antes de paginar, e `questions.cy.ts` verde
 • Testes automatizados do caso principal
 • Vídeo do teste anexado no PR</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="56" customHeight="1">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>#43</t>
-        </is>
-      </c>
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>feat(api): question bank CRUD with server-side filters</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
+    <row r="25" ht="95" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>#69</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>po: validate open scope items with the client</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>Validação de escopo</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>Processo e escopo</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>Heloísa Fogaça</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>heloisaFogaca</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="n">
+        <v>46311</v>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>A fazer</t>
+        </is>
+      </c>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>Pendência do README (cliente)</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="inlineStr">
+        <is>
+          <t>• Excel na importação/exportação: formato e colunas que o cliente usa hoje
+• Retorno do cartão-resposta ao aluno
+• Finalidade do e-mail do aluno
+• Alunos menores de idade
+• Respostas registradas em docs e no README, com a data
+• Issues afetadas (#42, #43, #46 e #82) avisadas com a resposta
+• Evidência (link, print ou vídeo) anexada na issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="108" customHeight="1">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>#84</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>docs: first architecture decision records in docs/adr</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>Documentação</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>Documentação</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>Priscila Torres</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>PrieTorres</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="n">
+        <v>46311</v>
+      </c>
+      <c r="H26" s="5" t="inlineStr">
+        <is>
+          <t>#31, #32, #83</t>
+        </is>
+      </c>
+      <c r="I26" s="5" t="inlineStr">
+        <is>
+          <t>A fazer</t>
+        </is>
+      </c>
+      <c r="J26" s="5" t="inlineStr">
+        <is>
+          <t>Modelo de documentação da disciplina</t>
+        </is>
+      </c>
+      <c r="K26" s="5" t="inlineStr">
+        <is>
+          <t>• ADR da escolha e da hospedagem do banco MySQL
+• ADR da estrutura em camadas da API (rota → controle → serviço → repositório → model)
+• ADR da autenticação, conforme a decisão com a professora (#83)
+• ADR do armazenamento das imagens das folhas, fora do banco
+• ADR de onde a API fica hospedada: serviço, plano gratuito e limites
+• Arquivos em `docs/adr/`, no formato Contexto, Decisão e Consequências, linkados na seção 6 do README
+• Arquivos numerados e com nome em inglês (`ADR-001-...md`)
+• Evidência (link, print ou vídeo) anexada na issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="134" customHeight="1">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>#45</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>feat: exams on the API, with the automatic draw on the server</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
         <is>
           <t>Desenvolvimento</t>
         </is>
       </c>
-      <c r="D23" s="5" t="inlineStr">
+      <c r="D27" s="5" t="inlineStr">
         <is>
           <t>Questões e provas</t>
         </is>
       </c>
-      <c r="E23" s="5" t="inlineStr">
+      <c r="E27" s="5" t="inlineStr">
         <is>
           <t>Cleberson Maia</t>
         </is>
       </c>
-      <c r="F23" s="5" t="inlineStr">
+      <c r="F27" s="5" t="inlineStr">
         <is>
           <t>maia202</t>
         </is>
       </c>
-      <c r="G23" s="6" t="n">
-        <v>46310</v>
-      </c>
-      <c r="H23" s="5" t="inlineStr">
-        <is>
-          <t>Auth</t>
-        </is>
-      </c>
-      <c r="I23" s="5" t="inlineStr">
+      <c r="G27" s="6" t="n">
+        <v>46312</v>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>#43, #44, #38, #32</t>
+        </is>
+      </c>
+      <c r="I27" s="5" t="inlineStr">
         <is>
           <t>A fazer</t>
         </is>
       </c>
-      <c r="J23" s="5" t="inlineStr">
+      <c r="J27" s="5" t="inlineStr">
         <is>
           <t>Plano da N2</t>
         </is>
       </c>
-      <c r="K23" s="5" t="inlineStr">
-        <is>
-          <t>• Criar/listar/editar/excluir (soft delete)
-• Filtros e paginação no servidor
+      <c r="K27" s="5" t="inlineStr">
+        <is>
+          <t>• As 7 rotas de prova respondem, todas exigem login, e prova de outro professor responde 404
+• Exam persistido com o embaralhamento que as versões vão herdar: `allowShuffleAlternatives` por questão (RF13), `defaultShuffleQuestions` e `defaultShuffleAlternatives` (RF17), além de `order` e `score` (o `ExamVersion` com `layout` nasce na geração da aplicação, na #46)
+• O servidor recusa mais de 20 questões, questão repetida e questão de outro professor, e aceita questão já excluída do banco que a prova usava
+• Título repetido responde 409 com a mensagem de hoje, inclusive contra prova arquivada
+• `status` nunca vem do corpo: nasce `draft`, arquivar grava `closed` e restaurar volta para `draft`
+• Geração automática no servidor (`POST /exams/draw`): só questões ativas do professor, com todas as tags pedidas, sem repetir as que já estão na prova
+• Telas de provas (P8, P9, P9b e P10) usam a API, e o formulário e o detalhe mostram o enunciado de toda questão da prova, mesmo fora da primeira página do banco
+• Testes com supertest para criar, editar, arquivar, restaurar, título repetido, acesso de outro professor e sorteio
 • Testes automatizados do caso principal
 • Vídeo do teste anexado no PR</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="56" customHeight="1">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>#44</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>feat(web): question bank screens on the API</t>
-        </is>
-      </c>
-      <c r="C24" s="5" t="inlineStr">
+    <row r="28" ht="212" customHeight="1">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>#46</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>feat: applications, exam versions and answer sheets with QR code</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
         <is>
           <t>Desenvolvimento</t>
         </is>
       </c>
-      <c r="D24" s="5" t="inlineStr">
-        <is>
-          <t>Questões e provas</t>
-        </is>
-      </c>
-      <c r="E24" s="5" t="inlineStr">
-        <is>
-          <t>Cleberson Maia</t>
-        </is>
-      </c>
-      <c r="F24" s="5" t="inlineStr">
-        <is>
-          <t>maia202</t>
-        </is>
-      </c>
-      <c r="G24" s="6" t="n">
-        <v>46311</v>
-      </c>
-      <c r="H24" s="5" t="inlineStr">
-        <is>
-          <t>Questions API</t>
-        </is>
-      </c>
-      <c r="I24" s="5" t="inlineStr">
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>Turmas e aplicações</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>Jeliel Nunes</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>Jeliell</t>
+        </is>
+      </c>
+      <c r="G28" s="6" t="n">
+        <v>46313</v>
+      </c>
+      <c r="H28" s="5" t="inlineStr">
+        <is>
+          <t>#31, #32, #40, #38, #41, #45</t>
+        </is>
+      </c>
+      <c r="I28" s="5" t="inlineStr">
         <is>
           <t>A fazer</t>
         </is>
       </c>
-      <c r="J24" s="5" t="inlineStr">
+      <c r="J28" s="5" t="inlineStr">
         <is>
           <t>Plano da N2</t>
         </is>
       </c>
-      <c r="K24" s="5" t="inlineStr">
-        <is>
-          <t>• Lista e criar/editar usam a API
-• Filtros chamam o servidor
-• Testes automatizados do caso principal
+      <c r="K28" s="5" t="inlineStr">
+        <is>
+          <t>• Application e ExamAssignment: as rotas de `Application` (listar com filtros, ver, criar, editar, arquivar, restaurar) respondem e exigem login; `ExamAssignment` continua só como tabela do contrato, sem rota
+• Aplicação, versão, folha ou PDF de outro professor responde 404 (teste com dois professores)
+• Criar aplicação recusa prova arquivada e turma arquivada
+• Gerar grava as versões com `layout` e uma `AnswerSheet` por aluno ativo da turma, inclusive quando a prova tem questão excluída depois
+• AnswerSheet com sheetNumber e code aleatório de 128 bits: `sheetNumber` sequencial na aplicação e `code` de 26 caracteres (130 bits), gerado no servidor e único no banco
+• PDF consolidado gerado de verdade, sem simulação, com um QR Code único por folha (RF23)
+• O cartão-resposta impresso traz os marcadores de canto e a grade de bolinhas em posições fixas e documentadas, que a leitura da #78 usa (referência: `docs/prova.jpg.jpeg`)
+• O QR Code leva `&lt;URL pública&gt;/r/&lt;code&gt;`, com a base vinda de variável de ambiente
+• No PDF, questão não quebra entre páginas (RF43) e prova com número ímpar de páginas ganha uma em branco (RF44)
+• Regenerar substitui versões, folhas e PDF, e o código antigo deixa de ser encontrado (RF24)
+• Gerar com folha já corrigida responde 409 e a tela mostra o motivo
+• Telas de aplicação e PDF usam a API: P11, P12, P13 e P14, incluindo publicar gabarito e liberar notas
+• "Liberar notas" fica bloqueado enquanto o gabarito da versão não for publicado, na tela P14 e no servidor
+• O modelo fixo `exemplos/prova-exemplo.html` sai da tela e "Baixar PDF" baixa o arquivo gerado
+• Testes automatizados do caso principal: supertest para criar, gerar, regenerar, recusar geração com correção e acesso de outro professor; teste unitário do que for regra nova; `applications.cy.ts` atualizado para o PDF real
 • Vídeo do teste anexado no PR</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="69" customHeight="1">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>#69</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="inlineStr">
-        <is>
-          <t>po: validate open scope items with the client</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>Validação de escopo</t>
-        </is>
-      </c>
-      <c r="D25" s="5" t="inlineStr">
-        <is>
-          <t>Processo e escopo</t>
-        </is>
-      </c>
-      <c r="E25" s="5" t="inlineStr">
-        <is>
-          <t>Heloísa Fogaça</t>
-        </is>
-      </c>
-      <c r="F25" s="5" t="inlineStr">
-        <is>
-          <t>heloisaFogaca</t>
-        </is>
-      </c>
-      <c r="G25" s="6" t="n">
-        <v>46311</v>
-      </c>
-      <c r="H25" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I25" s="5" t="inlineStr">
-        <is>
-          <t>A fazer</t>
-        </is>
-      </c>
-      <c r="J25" s="5" t="inlineStr">
-        <is>
-          <t>Pendência do README (cliente)</t>
-        </is>
-      </c>
-      <c r="K25" s="5" t="inlineStr">
-        <is>
-          <t>• Excel na importação/exportação
-• Retorno do cartão-resposta ao aluno
-• Finalidade do e-mail do aluno e alunos menores de idade
-• Respostas registradas em docs e no README
-• Evidência (link, print ou vídeo) anexada na issue</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="82" customHeight="1">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>#84</t>
-        </is>
-      </c>
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>docs: first architecture decision records in docs/adr</t>
-        </is>
-      </c>
-      <c r="C26" s="5" t="inlineStr">
-        <is>
-          <t>Documentação</t>
-        </is>
-      </c>
-      <c r="D26" s="5" t="inlineStr">
-        <is>
-          <t>Documentação</t>
-        </is>
-      </c>
-      <c r="E26" s="5" t="inlineStr">
-        <is>
-          <t>Priscila Torres</t>
-        </is>
-      </c>
-      <c r="F26" s="5" t="inlineStr">
-        <is>
-          <t>PrieTorres</t>
-        </is>
-      </c>
-      <c r="G26" s="6" t="n">
-        <v>46311</v>
-      </c>
-      <c r="H26" s="5" t="inlineStr">
-        <is>
-          <t>#31, #32, #83</t>
-        </is>
-      </c>
-      <c r="I26" s="5" t="inlineStr">
-        <is>
-          <t>A fazer</t>
-        </is>
-      </c>
-      <c r="J26" s="5" t="inlineStr">
-        <is>
-          <t>Modelo de documentação da disciplina</t>
-        </is>
-      </c>
-      <c r="K26" s="5" t="inlineStr">
-        <is>
-          <t>• ADR da escolha e da hospedagem do banco MySQL
-• ADR da estrutura em camadas da API (rota → controle → serviço → repositório → model)
-• ADR da autenticação, conforme a decisão com a professora
-• ADR do armazenamento das imagens das folhas, fora do banco
-• Arquivos em `docs/adr/`, no formato Contexto, Decisão e Consequências, linkados na seção 6 do README
-• Evidência (link, print ou vídeo) anexada na issue</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="69" customHeight="1">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>#45</t>
-        </is>
-      </c>
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>feat: exams and versions with persisted shuffle</t>
-        </is>
-      </c>
-      <c r="C27" s="5" t="inlineStr">
-        <is>
-          <t>Desenvolvimento</t>
-        </is>
-      </c>
-      <c r="D27" s="5" t="inlineStr">
-        <is>
-          <t>Questões e provas</t>
-        </is>
-      </c>
-      <c r="E27" s="5" t="inlineStr">
-        <is>
-          <t>Cleberson Maia</t>
-        </is>
-      </c>
-      <c r="F27" s="5" t="inlineStr">
-        <is>
-          <t>maia202</t>
-        </is>
-      </c>
-      <c r="G27" s="6" t="n">
-        <v>46312</v>
-      </c>
-      <c r="H27" s="5" t="inlineStr">
-        <is>
-          <t>Questions API</t>
-        </is>
-      </c>
-      <c r="I27" s="5" t="inlineStr">
-        <is>
-          <t>A fazer</t>
-        </is>
-      </c>
-      <c r="J27" s="5" t="inlineStr">
-        <is>
-          <t>Plano da N2</t>
-        </is>
-      </c>
-      <c r="K27" s="5" t="inlineStr">
-        <is>
-          <t>• Exam e ExamVersion com layout persistido
-• Geração automática no servidor
-• Telas de provas usam a API
-• Testes automatizados do caso principal
-• Vídeo do teste anexado no PR</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="56" customHeight="1">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>#64</t>
-        </is>
-      </c>
-      <c r="B28" s="5" t="inlineStr">
-        <is>
-          <t>review: code review of the question bank and exams pull requests</t>
-        </is>
-      </c>
-      <c r="C28" s="5" t="inlineStr">
-        <is>
-          <t>Code review</t>
-        </is>
-      </c>
-      <c r="D28" s="5" t="inlineStr">
-        <is>
-          <t>Questões e provas</t>
-        </is>
-      </c>
-      <c r="E28" s="5" t="inlineStr">
-        <is>
-          <t>Jeliel Nunes</t>
-        </is>
-      </c>
-      <c r="F28" s="5" t="inlineStr">
-        <is>
-          <t>Jeliell</t>
-        </is>
-      </c>
-      <c r="G28" s="6" t="n">
-        <v>46312</v>
-      </c>
-      <c r="H28" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I28" s="5" t="inlineStr">
-        <is>
-          <t>A fazer</t>
-        </is>
-      </c>
-      <c r="J28" s="5" t="inlineStr">
-        <is>
-          <t>Plano da N2</t>
-        </is>
-      </c>
-      <c r="K28" s="5" t="inlineStr">
-        <is>
-          <t>• Revisar e aprovar ou pedir mudanças nos PRs de question bank and exams
-• Conferir o vídeo do teste contra o checklist da issue
-• Prints das revisões no diário
-• Evidência (link, print ou vídeo) anexada na issue</t>
         </is>
       </c>
     </row>
     <row r="29" ht="82" customHeight="1">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>#46</t>
+          <t>#62</t>
         </is>
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>feat: applications, assignments and answer sheets with QR code</t>
+          <t>qa: exploratory test of question bank and exams on the real database</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>Desenvolvimento</t>
+          <t>QA exploratório</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>Turmas e aplicações</t>
+          <t>Questões e provas</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -2066,7 +2152,7 @@
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t>Exams, classes</t>
+          <t>#44, #45, #43, #40</t>
         </is>
       </c>
       <c r="I29" s="5" t="inlineStr">
@@ -2081,125 +2167,8 @@
       </c>
       <c r="K29" s="5" t="inlineStr">
         <is>
-          <t>• Application e ExamAssignment
-• AnswerSheet com sheetNumber e code aleatório de 128 bits
-• Telas de aplicação e PDF usam a API
-• Testes automatizados do caso principal
-• Vídeo do teste anexado no PR
-• PDF consolidado gerado de verdade, sem simulação, com um QR Code único por folha (RF23)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="56" customHeight="1">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>#60</t>
-        </is>
-      </c>
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>review: code review of the classes and applications pull requests</t>
-        </is>
-      </c>
-      <c r="C30" s="5" t="inlineStr">
-        <is>
-          <t>Code review</t>
-        </is>
-      </c>
-      <c r="D30" s="5" t="inlineStr">
-        <is>
-          <t>Turmas e aplicações</t>
-        </is>
-      </c>
-      <c r="E30" s="5" t="inlineStr">
-        <is>
-          <t>Heloísa Fogaça</t>
-        </is>
-      </c>
-      <c r="F30" s="5" t="inlineStr">
-        <is>
-          <t>heloisaFogaca</t>
-        </is>
-      </c>
-      <c r="G30" s="6" t="n">
-        <v>46313</v>
-      </c>
-      <c r="H30" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I30" s="5" t="inlineStr">
-        <is>
-          <t>A fazer</t>
-        </is>
-      </c>
-      <c r="J30" s="5" t="inlineStr">
-        <is>
-          <t>Plano da N2</t>
-        </is>
-      </c>
-      <c r="K30" s="5" t="inlineStr">
-        <is>
-          <t>• Revisar e aprovar ou pedir mudanças nos PRs de classes and applications
-• Conferir o vídeo do teste contra o checklist da issue
-• Prints das revisões no diário
-• Evidência (link, print ou vídeo) anexada na issue</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="69" customHeight="1">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t>#62</t>
-        </is>
-      </c>
-      <c r="B31" s="5" t="inlineStr">
-        <is>
-          <t>qa: exploratory test of question bank and exams on the real database</t>
-        </is>
-      </c>
-      <c r="C31" s="5" t="inlineStr">
-        <is>
-          <t>QA exploratório</t>
-        </is>
-      </c>
-      <c r="D31" s="5" t="inlineStr">
-        <is>
-          <t>Questões e provas</t>
-        </is>
-      </c>
-      <c r="E31" s="5" t="inlineStr">
-        <is>
-          <t>Jeliel Nunes</t>
-        </is>
-      </c>
-      <c r="F31" s="5" t="inlineStr">
-        <is>
-          <t>Jeliell</t>
-        </is>
-      </c>
-      <c r="G31" s="6" t="n">
-        <v>46313</v>
-      </c>
-      <c r="H31" s="5" t="inlineStr">
-        <is>
-          <t>Integração de question bank and exams</t>
-        </is>
-      </c>
-      <c r="I31" s="5" t="inlineStr">
-        <is>
-          <t>A fazer</t>
-        </is>
-      </c>
-      <c r="J31" s="5" t="inlineStr">
-        <is>
-          <t>Plano da N2</t>
-        </is>
-      </c>
-      <c r="K31" s="5" t="inlineStr">
-        <is>
           <t>• Testar criar/listar/editar/excluir e casos de borda (banco de questões, provas, geração automática)
+• Testar o isolamento com um segundo professor: nada de A aparece para B, e URL de A mostra "não encontrada"
 • Abrir uma issue Bug por problema, com vídeo
 • Conferir que nada some ao editar e que não há dado simulado
 • Retestar os bugs corrigidos
@@ -2207,35 +2176,161 @@
         </is>
       </c>
     </row>
-    <row r="32" ht="69" customHeight="1">
+    <row r="30" ht="69" customHeight="1">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>#64</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>review: code review of the question bank and exams pull requests</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>Code review</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>Questões e provas</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>Jeliel Nunes</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>Jeliell</t>
+        </is>
+      </c>
+      <c r="G30" s="6" t="n">
+        <v>46313</v>
+      </c>
+      <c r="H30" s="5" t="inlineStr">
+        <is>
+          <t>#43, #44, #45</t>
+        </is>
+      </c>
+      <c r="I30" s="5" t="inlineStr">
+        <is>
+          <t>A fazer</t>
+        </is>
+      </c>
+      <c r="J30" s="5" t="inlineStr">
+        <is>
+          <t>Plano da N2</t>
+        </is>
+      </c>
+      <c r="K30" s="5" t="inlineStr">
+        <is>
+          <t>• Revisar e aprovar ou pedir mudanças nos PRs de question bank and exams (#43, #44 e #45), com comentário no código, e não só aprovação
+• Rodar cada PR localmente: tipos, testes unitários, Cypress e, na #43 e na #45, os testes da API
+• Conferir o vídeo do teste contra o checklist da issue
+• Prints das revisões no diário
+• Evidência (link, print ou vídeo) anexada na issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="173" customHeight="1">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>#47</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>feat(api): answer sheet upload and correction review</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>Desenvolvimento</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>Correção, painel e relatórios</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>Fabricio da Silva</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>fabriciojrr</t>
+        </is>
+      </c>
+      <c r="G31" s="6" t="n">
+        <v>46314</v>
+      </c>
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t>#31, #32, #40, #46, #84</t>
+        </is>
+      </c>
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t>A fazer</t>
+        </is>
+      </c>
+      <c r="J31" s="5" t="inlineStr">
+        <is>
+          <t>Plano da N2</t>
+        </is>
+      </c>
+      <c r="K31" s="5" t="inlineStr">
+        <is>
+          <t>• Upload aceita só imagem (pelo tipo real do arquivo, não pela extensão), com limite de 10 MB, e guarda o arquivo fora do banco: na tabela fica só `imageUrl`
+• A imagem só é entregue ao professor dono da aplicação, nunca por um endereço público
+• O envio devolve o resultado da leitura (`READ`, `QR_NOT_RECOGNIZED` ou `READ_FAILED`), e nada vira `Correction` antes da confirmação
+• Toda falha de leitura fica registrada no `ActivityLog`, com a referência da imagem e sem dado pessoal, e aparece em `GET /applications/:id/read-failures`
+• Correction por folha, gravada a partir de um envio (`source: "IMAGE_UPLOAD"`) ou com lançamento manual, sem imagem (`source: "MANUAL"`, RF30)
+• Atribuição de aluno em folha sem identificação (RF31), com `409` quando o mesmo aluno aparece duas vezes na mesma versão
+• Nota final só após confirmação do professor: nenhuma leitura cria `Correction`, e `DONE` só sai com `finalize: true` e todas as discursivas com nota (RF28, RF47)
+• O servidor recalcula acerto, nota por questão, `totalScore` e `status`, e ignora esses valores quando vêm do cliente
+• Um professor não vê nem altera correção, envio ou imagem de outro (404)
+• O PATCH mescla e não apaga o campo que não foi enviado, inclusive `clientCorrectionId` e `syncStatus`
+• Testes com supertest para: envio válido, arquivo que não é imagem, arquivo acima do limite, correção manual, revisão parcial e final, atribuição com conflito e acesso de outro professor
+• Testes automatizados do caso principal
+• Vídeo do teste anexado no PR (chamando as rotas pelo Postman ou Insomnia, ou rodando os testes)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="95" customHeight="1">
       <c r="A32" s="4" t="inlineStr">
         <is>
-          <t>#47</t>
+          <t>#58</t>
         </is>
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>feat(api): answer sheet upload and correction review</t>
+          <t>qa: exploratory test of classes and applications on the real database</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>Desenvolvimento</t>
+          <t>QA exploratório</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>Correção, painel e relatórios</t>
+          <t>Turmas e aplicações</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>Fabricio da Silva</t>
+          <t>Heloísa Fogaça</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>fabriciojrr</t>
+          <t>heloisaFogaca</t>
         </is>
       </c>
       <c r="G32" s="6" t="n">
@@ -2243,7 +2338,7 @@
       </c>
       <c r="H32" s="5" t="inlineStr">
         <is>
-          <t>Applications</t>
+          <t>#41, #42, #46</t>
         </is>
       </c>
       <c r="I32" s="5" t="inlineStr">
@@ -2258,66 +2353,9 @@
       </c>
       <c r="K32" s="5" t="inlineStr">
         <is>
-          <t>• Upload aceita só imagem, com limite de tamanho, fora do banco
-• Correction por folha, lançamento manual e atribuição
-• Nota final só após confirmação do professor
-• Testes automatizados do caso principal
-• Vídeo do teste anexado no PR</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="69" customHeight="1">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t>#58</t>
-        </is>
-      </c>
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>qa: exploratory test of classes and applications on the real database</t>
-        </is>
-      </c>
-      <c r="C33" s="5" t="inlineStr">
-        <is>
-          <t>QA exploratório</t>
-        </is>
-      </c>
-      <c r="D33" s="5" t="inlineStr">
-        <is>
-          <t>Turmas e aplicações</t>
-        </is>
-      </c>
-      <c r="E33" s="5" t="inlineStr">
-        <is>
-          <t>Heloísa Fogaça</t>
-        </is>
-      </c>
-      <c r="F33" s="5" t="inlineStr">
-        <is>
-          <t>heloisaFogaca</t>
-        </is>
-      </c>
-      <c r="G33" s="6" t="n">
-        <v>46314</v>
-      </c>
-      <c r="H33" s="5" t="inlineStr">
-        <is>
-          <t>Integração de classes and applications</t>
-        </is>
-      </c>
-      <c r="I33" s="5" t="inlineStr">
-        <is>
-          <t>A fazer</t>
-        </is>
-      </c>
-      <c r="J33" s="5" t="inlineStr">
-        <is>
-          <t>Plano da N2</t>
-        </is>
-      </c>
-      <c r="K33" s="5" t="inlineStr">
-        <is>
           <t>• Testar criar/listar/editar/excluir e casos de borda (turmas, alunos, importação, aplicações, PDF)
+• Testar o isolamento com dois professores: um não vê nem altera turma ou aplicação do outro
+• Conferir o PDF: um QR Code por folha, questão sem quebra de página e página em branco quando ímpar
 • Abrir uma issue Bug por problema, com vídeo
 • Conferir que nada some ao editar e que não há dado simulado
 • Retestar os bugs corrigidos
@@ -2325,119 +2363,123 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="69" customHeight="1">
-      <c r="A34" s="4" t="inlineStr">
+    <row r="33" ht="95" customHeight="1">
+      <c r="A33" s="4" t="inlineStr">
         <is>
           <t>#63</t>
         </is>
       </c>
-      <c r="B34" s="5" t="inlineStr">
+      <c r="B33" s="5" t="inlineStr">
         <is>
           <t>test(e2e): Cypress coverage for question bank and exams against the API</t>
         </is>
       </c>
-      <c r="C34" s="5" t="inlineStr">
+      <c r="C33" s="5" t="inlineStr">
         <is>
           <t>Teste automatizado</t>
         </is>
       </c>
-      <c r="D34" s="5" t="inlineStr">
+      <c r="D33" s="5" t="inlineStr">
         <is>
           <t>Questões e provas</t>
         </is>
       </c>
-      <c r="E34" s="5" t="inlineStr">
+      <c r="E33" s="5" t="inlineStr">
         <is>
           <t>Cleberson Maia</t>
         </is>
       </c>
-      <c r="F34" s="5" t="inlineStr">
+      <c r="F33" s="5" t="inlineStr">
         <is>
           <t>maia202</t>
         </is>
       </c>
-      <c r="G34" s="6" t="n">
+      <c r="G33" s="6" t="n">
         <v>46314</v>
       </c>
-      <c r="H34" s="5" t="inlineStr">
-        <is>
-          <t>Exploratory test of question bank and exams</t>
-        </is>
-      </c>
-      <c r="I34" s="5" t="inlineStr">
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t>#62, #44, #45, #40, #39</t>
+        </is>
+      </c>
+      <c r="I33" s="5" t="inlineStr">
         <is>
           <t>A fazer</t>
         </is>
       </c>
-      <c r="J34" s="5" t="inlineStr">
+      <c r="J33" s="5" t="inlineStr">
         <is>
           <t>Plano da N2</t>
         </is>
       </c>
-      <c r="K34" s="5" t="inlineStr">
-        <is>
-          <t>• Specs de banco de questões, provas, geração automática cobrindo fluxo feliz, erro e estado vazio
-• Seletores por nome acessível, nunca por tag ou índice
+      <c r="K33" s="5" t="inlineStr">
+        <is>
+          <t>• Specs de banco de questões, provas e geração automática (`questions.cy.ts` e `exams.cy.ts`) rodando contra a API e cobrindo fluxo feliz, erro e estado vazio de P6, P7, P8, P9, P9b e P10
+• Cada teste cria os próprios dados pela API e entra com o professor do próprio run, sem depender da semente da N1
+• Seletores por nome acessível, nunca presos à tag nem escolhendo item por índice (índice só para conferir ordem)
+• Um cenário para cada bug encontrado na #62
 • Suíte inteira verde no CI
 • Testes automatizados do caso principal
 • Vídeo do teste anexado no PR</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="108" customHeight="1">
-      <c r="A35" s="4" t="inlineStr">
+    <row r="34" ht="134" customHeight="1">
+      <c r="A34" s="4" t="inlineStr">
         <is>
           <t>#78</t>
         </is>
       </c>
-      <c r="B35" s="5" t="inlineStr">
+      <c r="B34" s="5" t="inlineStr">
         <is>
           <t>feat: read the QR code and the marks from the sheet photo (RF27)</t>
         </is>
       </c>
-      <c r="C35" s="5" t="inlineStr">
+      <c r="C34" s="5" t="inlineStr">
         <is>
           <t>Desenvolvimento</t>
         </is>
       </c>
-      <c r="D35" s="5" t="inlineStr">
+      <c r="D34" s="5" t="inlineStr">
         <is>
           <t>Correção, painel e relatórios</t>
         </is>
       </c>
-      <c r="E35" s="5" t="inlineStr">
+      <c r="E34" s="5" t="inlineStr">
         <is>
           <t>Priscila Torres</t>
         </is>
       </c>
-      <c r="F35" s="5" t="inlineStr">
+      <c r="F34" s="5" t="inlineStr">
         <is>
           <t>PrieTorres</t>
         </is>
       </c>
-      <c r="G35" s="6" t="n">
+      <c r="G34" s="6" t="n">
         <v>46314</v>
       </c>
-      <c r="H35" s="5" t="inlineStr">
-        <is>
-          <t>#46, #47</t>
-        </is>
-      </c>
-      <c r="I35" s="5" t="inlineStr">
+      <c r="H34" s="5" t="inlineStr">
+        <is>
+          <t>#46, #47, #84</t>
+        </is>
+      </c>
+      <c r="I34" s="5" t="inlineStr">
         <is>
           <t>A fazer</t>
         </is>
       </c>
-      <c r="J35" s="5" t="inlineStr">
+      <c r="J34" s="5" t="inlineStr">
         <is>
           <t>Feedback da N1</t>
         </is>
       </c>
-      <c r="K35" s="5" t="inlineStr">
-        <is>
-          <t>• Decisão de onde a leitura roda (navegador ou servidor) registrada como ADR em `docs/adr/`
+      <c r="K34" s="5" t="inlineStr">
+        <is>
+          <t>• Decisão de onde a leitura roda (navegador ou servidor) registrada como ADR em `docs/adr/`, com as bibliotecas candidatas comparadas
 • O QR Code da foto identifica a folha pelo `AnswerSheet.code`
-• Marcações lidas pelas posições gravadas em `ExamVersion.layout`, devolvendo a alternativa marcada em cada objetiva
+• Código de outra aplicação ou de PDF regenerado é tratado como "QR não reconhecido"
+• Marcações lidas nas posições do cartão impresso e traduzidas pelo `ExamVersion.layout`, devolvendo a alternativa marcada em cada objetiva
+• Questão em branco ou com mais de uma marca volta sem alternativa, para o professor decidir na revisão
 • Folha com QR ilegível fica como "QR não reconhecido" e segue para a correção manual (RF30)
 • A leitura nunca confirma a nota sozinha: sempre abre a revisão (RF28)
 • Testado com fotos de folhas impressas de verdade, tiradas no celular
@@ -2446,153 +2488,223 @@
         </is>
       </c>
     </row>
-    <row r="36" ht="69" customHeight="1">
-      <c r="A36" s="4" t="inlineStr">
-        <is>
-          <t>#27</t>
-        </is>
-      </c>
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t>Diagrama de Atividade</t>
-        </is>
-      </c>
-      <c r="C36" s="5" t="inlineStr">
+    <row r="35" ht="95" customHeight="1">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>#28</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>Diagrama de Classe</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
         <is>
           <t>Documentação</t>
         </is>
       </c>
-      <c r="D36" s="5" t="inlineStr">
+      <c r="D35" s="5" t="inlineStr">
         <is>
           <t>Documentação</t>
         </is>
       </c>
-      <c r="E36" s="5" t="inlineStr">
-        <is>
-          <t>Jeliel Nunes</t>
-        </is>
-      </c>
-      <c r="F36" s="5" t="inlineStr">
-        <is>
-          <t>Jeliell</t>
-        </is>
-      </c>
-      <c r="G36" s="6" t="n">
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>Cleberson Maia</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>maia202</t>
+        </is>
+      </c>
+      <c r="G35" s="6" t="n">
         <v>46315</v>
       </c>
-      <c r="H36" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I36" s="5" t="inlineStr">
-        <is>
-          <t>Em andamento</t>
-        </is>
-      </c>
-      <c r="J36" s="5" t="inlineStr">
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>#32</t>
+        </is>
+      </c>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>Em revisão</t>
+        </is>
+      </c>
+      <c r="J35" s="5" t="inlineStr">
         <is>
           <t>Issue já existente</t>
         </is>
       </c>
-      <c r="K36" s="5" t="inlineStr">
-        <is>
-          <t>• Fonte e imagem do diagrama em `docs/uml/`, e não só o `.docx` anexado nos comentários
-• Fluxo de correção atualizado para a N2: a foto passa pela API, e a correção é gravada no MySQL
-• Linha cheia no lugar do tracejado no que a N2 implementar: correção manual (RF30) e nota só depois da confirmação do professor (RNF07, RF47)
-• PR com `Closes #27` e label `docs`
-• Evidência (link, print ou vídeo) anexada na issue</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="69" customHeight="1">
-      <c r="A37" s="4" t="inlineStr">
-        <is>
-          <t>#28</t>
-        </is>
-      </c>
-      <c r="B37" s="5" t="inlineStr">
-        <is>
-          <t>Diagrama de Classe</t>
-        </is>
-      </c>
-      <c r="C37" s="5" t="inlineStr">
-        <is>
-          <t>Documentação</t>
-        </is>
-      </c>
-      <c r="D37" s="5" t="inlineStr">
-        <is>
-          <t>Documentação</t>
-        </is>
-      </c>
-      <c r="E37" s="5" t="inlineStr">
-        <is>
-          <t>Cleberson Maia</t>
-        </is>
-      </c>
-      <c r="F37" s="5" t="inlineStr">
-        <is>
-          <t>maia202</t>
-        </is>
-      </c>
-      <c r="G37" s="6" t="n">
-        <v>46315</v>
-      </c>
-      <c r="H37" s="5" t="inlineStr">
-        <is>
-          <t>#32</t>
-        </is>
-      </c>
-      <c r="I37" s="5" t="inlineStr">
-        <is>
-          <t>Em revisão</t>
-        </is>
-      </c>
-      <c r="J37" s="5" t="inlineStr">
-        <is>
-          <t>Issue já existente</t>
-        </is>
-      </c>
-      <c r="K37" s="5" t="inlineStr">
-        <is>
-          <t>• Fonte (`.puml`) e imagem em `docs/uml/`
-• Entidades e campos iguais aos do `docs/Modelo_de_Dados.md`
+      <c r="K35" s="5" t="inlineStr">
+        <is>
+          <t>• Fonte (`.puml`) e imagem em `docs/uml/`, com nome em inglês (ex.: `class-diagram.puml` e `class-diagram.png`)
+• Entidades e campos iguais aos do `docs/Modelo_de_Dados.md`, com todas as linhas da tabela do comentário de 09/10 resolvidas
+• Elementos reservados para escopo futuro presentes no diagrama
+• Relação entre `Exam` e `Question` desenhada
 • Classes conferidas com as entidades do banco (#32)
 • PR com `Closes #28` e label `docs`
 • Evidência (link, print ou vídeo) anexada na issue</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="69" customHeight="1">
+    <row r="36" ht="121" customHeight="1">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>#48</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>feat(web): grading screens with real upload</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>Desenvolvimento</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>Correção, painel e relatórios</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>Fabricio da Silva</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t>fabriciojrr</t>
+        </is>
+      </c>
+      <c r="G36" s="6" t="n">
+        <v>46315</v>
+      </c>
+      <c r="H36" s="5" t="inlineStr">
+        <is>
+          <t>#47, #38</t>
+        </is>
+      </c>
+      <c r="I36" s="5" t="inlineStr">
+        <is>
+          <t>A fazer</t>
+        </is>
+      </c>
+      <c r="J36" s="5" t="inlineStr">
+        <is>
+          <t>Plano da N2</t>
+        </is>
+      </c>
+      <c r="K36" s="5" t="inlineStr">
+        <is>
+          <t>• Enviar, revisar e pendentes usam a API: P15, P16 e P17 sem `localStorage` e sem leitura simulada
+• Imagens de demonstração removidas: `public/demo-sheets`, `DEMO_SHEET_IMAGES`, `DEMO_SHEET` e os textos sobre leitura simulada
+• Botão "Fotografar folha" abre a câmera do celular (`capture`), uma folha por vez em sequência (P15)
+• Botão "Inserir correção manualmente", sem imagem (RF30), abre a P16 vazia para a folha escolhida
+• A lista da P15 mostra o status de cada folha (Processando, Lido, QR não reconhecido, Falha na leitura) e marca as que estão em andamento (RF48)
+• A revisão mostra a foto enviada, com as questões e as letras na ordem impressa daquela versão (`ExamVersion.layout`)
+• O tour da P15 descreve a tela nova e aponta para elementos que existem
+• Testes automatizados do caso principal
+• Vídeo do teste anexado no PR (com um celular fotografando uma folha)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="134" customHeight="1">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>#49</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>feat: public QR lookup on the API</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>Desenvolvimento</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>Acesso e consulta pública</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>Heloísa Fogaça</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>heloisaFogaca</t>
+        </is>
+      </c>
+      <c r="G37" s="6" t="n">
+        <v>46315</v>
+      </c>
+      <c r="H37" s="5" t="inlineStr">
+        <is>
+          <t>#31, #38, #46, #47</t>
+        </is>
+      </c>
+      <c r="I37" s="5" t="inlineStr">
+        <is>
+          <t>A fazer</t>
+        </is>
+      </c>
+      <c r="J37" s="5" t="inlineStr">
+        <is>
+          <t>Plano da N2</t>
+        </is>
+      </c>
+      <c r="K37" s="5" t="inlineStr">
+        <is>
+          <t>• Rota pública `GET /public/sheets/:code` responde sem login e busca só por `AnswerSheet.code`
+• Rate limit de 30 requisições por minuto por IP, com 429 e `Retry-After`, e a tela mostra mensagem própria
+• A resposta é só o `PublicLookup`, sem dados de outros alunos e sem campos internos da correção
+• Página do QR lê do banco, por um repositório público, sem os repositórios do professor
+• Code inválido mostra mensagem "QR inválido", com resposta idêntica para código desconhecido e para folha de PDF regenerado
+• Os quatro estados seguem os dois níveis de liberação, e a nota nunca aparece sem o gabarito
+• Correção em andamento (`IN_PROGRESS`) não mostra nota
+• Testes com supertest para os quatro estados, código inválido, PDF regenerado, correção em andamento, 429 e resposta sem nome de outro aluno
+• Testes automatizados do caso principal
+• Vídeo do teste anexado no PR</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="108" customHeight="1">
       <c r="A38" s="4" t="inlineStr">
         <is>
-          <t>#29</t>
+          <t>#59</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>Diagrama de Sequência</t>
+          <t>test(e2e): Cypress coverage for classes and applications against the API</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>Documentação</t>
+          <t>Teste automatizado</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>Documentação</t>
+          <t>Turmas e aplicações</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>Cleberson Maia</t>
+          <t>Jeliel Nunes</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>maia202</t>
+          <t>Jeliell</t>
         </is>
       </c>
       <c r="G38" s="6" t="n">
@@ -2600,433 +2712,764 @@
       </c>
       <c r="H38" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#58, #42, #46, #40, #39</t>
         </is>
       </c>
       <c r="I38" s="5" t="inlineStr">
         <is>
+          <t>A fazer</t>
+        </is>
+      </c>
+      <c r="J38" s="5" t="inlineStr">
+        <is>
+          <t>Plano da N2</t>
+        </is>
+      </c>
+      <c r="K38" s="5" t="inlineStr">
+        <is>
+          <t>• Specs de turmas, alunos, importação, aplicações, PDF cobrindo fluxo feliz, erro e estado vazio
+• A suíte roda contra a API e um banco de teste, com login e dados preparados pelo próprio teste, sem depender do `localStorage` nem do seed da N1
+• Os testes do modelo fixo do PDF foram trocados por testes do PDF gerado
+• Isolamento coberto: o professor B não abre turma nem aplicação do professor A
+• Seletores por nome acessível, nunca por tag ou índice, inclusive os existentes da tabela acima
+• Suíte inteira verde no CI
+• Testes automatizados do caso principal
+• Vídeo do teste anexado no PR</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="82" customHeight="1">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>#27</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>Diagrama de Atividade</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>Documentação</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>Documentação</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>Jeliel Nunes</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="inlineStr">
+        <is>
+          <t>Jeliell</t>
+        </is>
+      </c>
+      <c r="G39" s="6" t="n">
+        <v>46316</v>
+      </c>
+      <c r="H39" s="5" t="inlineStr">
+        <is>
+          <t>#47, #48, #78</t>
+        </is>
+      </c>
+      <c r="I39" s="5" t="inlineStr">
+        <is>
           <t>Em andamento</t>
         </is>
       </c>
-      <c r="J38" s="5" t="inlineStr">
+      <c r="J39" s="5" t="inlineStr">
         <is>
           <t>Issue já existente</t>
         </is>
       </c>
-      <c r="K38" s="5" t="inlineStr">
+      <c r="K39" s="5" t="inlineStr">
+        <is>
+          <t>• Fonte e imagem do diagrama em `docs/uml/`, com nome em inglês, e não só o `.docx` anexado nos comentários
+• Fluxo de correção atualizado para a N2: a foto passa pela API, e a correção é gravada no MySQL
+• Linha cheia no lugar do tracejado no que a N2 implementar: correção manual (RF30) e nota só depois da confirmação do professor (RNF07, RF47)
+• O que a N2 não implementou continua tracejado, com a legenda atualizada para a N2
+• PR com `Closes #27` e label `docs`
+• Evidência (link, print ou vídeo) anexada na issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="95" customHeight="1">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>#29</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>Diagrama de Sequência</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>Documentação</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>Documentação</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>Cleberson Maia</t>
+        </is>
+      </c>
+      <c r="F40" s="5" t="inlineStr">
+        <is>
+          <t>maia202</t>
+        </is>
+      </c>
+      <c r="G40" s="6" t="n">
+        <v>46316</v>
+      </c>
+      <c r="H40" s="5" t="inlineStr">
+        <is>
+          <t>#47, #83</t>
+        </is>
+      </c>
+      <c r="I40" s="5" t="inlineStr">
+        <is>
+          <t>Em andamento</t>
+        </is>
+      </c>
+      <c r="J40" s="5" t="inlineStr">
+        <is>
+          <t>Issue já existente</t>
+        </is>
+      </c>
+      <c r="K40" s="5" t="inlineStr">
         <is>
           <t>• Sequência do fluxo principal mostrando front → API → MySQL. Sugestão: enviar a folha e confirmar a correção.
+• Camadas da API aparecem (rota → controle → serviço → repositório), com as rotas que a #47 implementou
 • Mostrar o token de autenticação e a resposta de erro da API
-• Fonte (`.puml` ou Mermaid) e imagem em `docs/uml/`
+• A nota só passa a valer depois da confirmação do professor (RNF07)
+• Fonte (`.puml` ou Mermaid) e imagem em `docs/uml/`, com nome em inglês
 • PR com `Closes #29` e label `docs`
 • Evidência (link, print ou vídeo) anexada na issue</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="82" customHeight="1">
-      <c r="A39" s="4" t="inlineStr">
-        <is>
-          <t>#48</t>
-        </is>
-      </c>
-      <c r="B39" s="5" t="inlineStr">
-        <is>
-          <t>feat(web): grading screens with real upload</t>
-        </is>
-      </c>
-      <c r="C39" s="5" t="inlineStr">
+    <row r="41" ht="108" customHeight="1">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>#50</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>feat: dashboard, profile and reports on the API</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
         <is>
           <t>Desenvolvimento</t>
         </is>
       </c>
-      <c r="D39" s="5" t="inlineStr">
+      <c r="D41" s="5" t="inlineStr">
         <is>
           <t>Correção, painel e relatórios</t>
         </is>
       </c>
-      <c r="E39" s="5" t="inlineStr">
+      <c r="E41" s="5" t="inlineStr">
         <is>
           <t>Fabricio da Silva</t>
         </is>
       </c>
-      <c r="F39" s="5" t="inlineStr">
+      <c r="F41" s="5" t="inlineStr">
         <is>
           <t>fabriciojrr</t>
         </is>
       </c>
-      <c r="G39" s="6" t="n">
-        <v>46315</v>
-      </c>
-      <c r="H39" s="5" t="inlineStr">
-        <is>
-          <t>Correction API</t>
-        </is>
-      </c>
-      <c r="I39" s="5" t="inlineStr">
+      <c r="G41" s="6" t="n">
+        <v>46316</v>
+      </c>
+      <c r="H41" s="5" t="inlineStr">
+        <is>
+          <t>#47, #40, #38</t>
+        </is>
+      </c>
+      <c r="I41" s="5" t="inlineStr">
         <is>
           <t>A fazer</t>
         </is>
       </c>
-      <c r="J39" s="5" t="inlineStr">
+      <c r="J41" s="5" t="inlineStr">
         <is>
           <t>Plano da N2</t>
         </is>
       </c>
-      <c r="K39" s="5" t="inlineStr">
-        <is>
-          <t>• Enviar, revisar e pendentes usam a API
-• Imagens de demonstração removidas
-• Testes automatizados do caso principal
-• Vídeo do teste anexado no PR
-• Botão "Fotografar folha" abre a câmera do celular (`capture`), uma folha por vez em sequência (P15)
-• Botão "Inserir correção manualmente", sem imagem (RF30)</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="69" customHeight="1">
-      <c r="A40" s="4" t="inlineStr">
-        <is>
-          <t>#49</t>
-        </is>
-      </c>
-      <c r="B40" s="5" t="inlineStr">
-        <is>
-          <t>feat: public QR lookup on the API</t>
-        </is>
-      </c>
-      <c r="C40" s="5" t="inlineStr">
-        <is>
-          <t>Desenvolvimento</t>
-        </is>
-      </c>
-      <c r="D40" s="5" t="inlineStr">
-        <is>
-          <t>Acesso e consulta pública</t>
-        </is>
-      </c>
-      <c r="E40" s="5" t="inlineStr">
-        <is>
-          <t>Heloísa Fogaça</t>
-        </is>
-      </c>
-      <c r="F40" s="5" t="inlineStr">
-        <is>
-          <t>heloisaFogaca</t>
-        </is>
-      </c>
-      <c r="G40" s="6" t="n">
-        <v>46315</v>
-      </c>
-      <c r="H40" s="5" t="inlineStr">
-        <is>
-          <t>Correction API</t>
-        </is>
-      </c>
-      <c r="I40" s="5" t="inlineStr">
-        <is>
-          <t>A fazer</t>
-        </is>
-      </c>
-      <c r="J40" s="5" t="inlineStr">
-        <is>
-          <t>Plano da N2</t>
-        </is>
-      </c>
-      <c r="K40" s="5" t="inlineStr">
-        <is>
-          <t>• Rota pública por code, com rate limit e sem dados de outros alunos
-• Página do QR lê do banco
-• Code inválido mostra mensagem
+      <c r="K41" s="5" t="inlineStr">
+        <is>
+          <t>• Indicadores e relatórios calculados no servidor: painel, relatório da aplicação e relatório consolidado vêm das rotas próprias, sem listas de 1000 itens no navegador
+• Os números usam as funções de `lib/reports/statistics.ts`, e só correções `DONE` entram em média, mediana, desvio e distribuição
+• Prova, turma ou questão arquivada depois da aplicação continua aparecendo pelo nome no relatório
+• Perfil edita dados reais: nome, e-mail e tipo vêm da API, "Anonimizar minha conta" grava no banco e "Sair de todos os dispositivos" encerra todas as sessões
+• Um professor não vê números nem relatórios de outro (404 na aplicação de outro professor)
+• Testes com supertest para painel, relatório (com correção em andamento e sem nenhuma correção) e anonimização
 • Testes automatizados do caso principal
 • Vídeo do teste anexado no PR</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="56" customHeight="1">
-      <c r="A41" s="4" t="inlineStr">
+    <row r="42" ht="95" customHeight="1">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>#54</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>qa: exploratory test of access and public lookup on the real database</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>QA exploratório</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>Acesso e consulta pública</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>Fabricio da Silva</t>
+        </is>
+      </c>
+      <c r="F42" s="5" t="inlineStr">
+        <is>
+          <t>fabriciojrr</t>
+        </is>
+      </c>
+      <c r="G42" s="6" t="n">
+        <v>46316</v>
+      </c>
+      <c r="H42" s="5" t="inlineStr">
+        <is>
+          <t>#40, #49</t>
+        </is>
+      </c>
+      <c r="I42" s="5" t="inlineStr">
+        <is>
+          <t>A fazer</t>
+        </is>
+      </c>
+      <c r="J42" s="5" t="inlineStr">
+        <is>
+          <t>Plano da N2</t>
+        </is>
+      </c>
+      <c r="K42" s="5" t="inlineStr">
+        <is>
+          <t>• Testar login, cadastro, recuperar senha, sair, consulta por QR e privacidade, com os casos de borda dos passos 2 a 7
+• Abrir uma issue Bug por problema, com vídeo
+• Conferir que nada some ao editar: trocar a senha não altera nem esconde turmas, questões e provas do professor
+• Conferir que não há dado simulado (passo 8)
+• Conferir que a consulta pública não mostra dado de outro aluno, nem na resposta da rede
+• Retestar os bugs corrigidos
+• Evidência (link, print ou vídeo) anexada na issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="95" customHeight="1">
+      <c r="A43" s="4" t="inlineStr">
         <is>
           <t>#56</t>
         </is>
       </c>
-      <c r="B41" s="5" t="inlineStr">
+      <c r="B43" s="5" t="inlineStr">
         <is>
           <t>review: code review of the access and public lookup pull requests</t>
         </is>
       </c>
-      <c r="C41" s="5" t="inlineStr">
+      <c r="C43" s="5" t="inlineStr">
         <is>
           <t>Code review</t>
         </is>
       </c>
-      <c r="D41" s="5" t="inlineStr">
+      <c r="D43" s="5" t="inlineStr">
         <is>
           <t>Acesso e consulta pública</t>
         </is>
       </c>
-      <c r="E41" s="5" t="inlineStr">
+      <c r="E43" s="5" t="inlineStr">
         <is>
           <t>Fabricio da Silva</t>
         </is>
       </c>
-      <c r="F41" s="5" t="inlineStr">
+      <c r="F43" s="5" t="inlineStr">
         <is>
           <t>fabriciojrr</t>
         </is>
       </c>
-      <c r="G41" s="6" t="n">
-        <v>46315</v>
-      </c>
-      <c r="H41" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I41" s="5" t="inlineStr">
+      <c r="G43" s="6" t="n">
+        <v>46316</v>
+      </c>
+      <c r="H43" s="5" t="inlineStr">
+        <is>
+          <t>#40, #49</t>
+        </is>
+      </c>
+      <c r="I43" s="5" t="inlineStr">
         <is>
           <t>A fazer</t>
         </is>
       </c>
-      <c r="J41" s="5" t="inlineStr">
+      <c r="J43" s="5" t="inlineStr">
         <is>
           <t>Plano da N2</t>
         </is>
       </c>
-      <c r="K41" s="5" t="inlineStr">
-        <is>
-          <t>• Revisar e aprovar ou pedir mudanças nos PRs de access and public lookup
+      <c r="K43" s="5" t="inlineStr">
+        <is>
+          <t>• Revisar e aprovar ou pedir mudanças nos PRs da #40 e da #49, com comentário em cada um
+• Conferir o vídeo do teste contra o checklist da issue
+• Testes do PR rodados localmente
+• Nomes de campo conferidos contra `docs/Modelo_de_Dados.md`
+• Conferido, no código ou num teste, que recurso de outro professor responde 404 e que a consulta pública não expõe outro aluno
+• Prints das revisões no diário
+• Evidência (link, print ou vídeo) anexada na issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="121" customHeight="1">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>#71</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>docs: README v2 with integration status</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>Documentação</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>Documentação</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>Cleberson Maia</t>
+        </is>
+      </c>
+      <c r="F44" s="5" t="inlineStr">
+        <is>
+          <t>maia202</t>
+        </is>
+      </c>
+      <c r="G44" s="6" t="n">
+        <v>46316</v>
+      </c>
+      <c r="H44" s="5" t="inlineStr">
+        <is>
+          <t>#26, #27, #28, #29, #70, #84</t>
+        </is>
+      </c>
+      <c r="I44" s="5" t="inlineStr">
+        <is>
+          <t>A fazer</t>
+        </is>
+      </c>
+      <c r="J44" s="5" t="inlineStr">
+        <is>
+          <t>Plano da N2</t>
+        </is>
+      </c>
+      <c r="K44" s="5" t="inlineStr">
+        <is>
+          <t>• README na numeração do modelo da disciplina (`modelo_doc.md`), seções 1 a 14
+• Link do sistema hospedado no topo
+• Tabela do que está ligado ao banco, por área, com a issue de cada uma
+• Como rodar API + banco localmente
+• Nenhum trecho descreve dado simulado como se fosse o sistema atual
+• Links para diagramas e DER
+• Seção 3 (UML) com um parágrafo curto abaixo de cada diagrama
+• Seção 11 com a especificação da API (método, rota e descrição)
+• Evidência (link, print ou vídeo) anexada na issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="82" customHeight="1">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>#35</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>Testar passo e cenários da aplicação</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>QA exploratório</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>Sistema inteiro</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>Heloísa Fogaça</t>
+        </is>
+      </c>
+      <c r="F45" s="5" t="inlineStr">
+        <is>
+          <t>heloisaFogaca</t>
+        </is>
+      </c>
+      <c r="G45" s="6" t="n">
+        <v>46317</v>
+      </c>
+      <c r="H45" s="5" t="inlineStr">
+        <is>
+          <t>#52</t>
+        </is>
+      </c>
+      <c r="I45" s="5" t="inlineStr">
+        <is>
+          <t>A fazer</t>
+        </is>
+      </c>
+      <c r="J45" s="5" t="inlineStr">
+        <is>
+          <t>Issue já existente</t>
+        </is>
+      </c>
+      <c r="K45" s="5" t="inlineStr">
+        <is>
+          <t>• Link do documento de passos e onboarding colado nesta issue
+• Lista de cenários do documento escrita nesta issue
+• Passos do documento e do onboarding da aplicação seguidos na versão publicada, com o resultado de cada cenário anotado
+• Tour guiado conferido contra `docs/Tour_Guiado.md` nas telas que têm tour
+• Uma issue Bug por problema encontrado, com vídeo
+• Evidência (link, print ou vídeo) anexada na issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="147" customHeight="1">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>#51</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>chore(web): remove every simulated data source from production</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>Desenvolvimento</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>Infraestrutura e API</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>Priscila Torres</t>
+        </is>
+      </c>
+      <c r="F46" s="5" t="inlineStr">
+        <is>
+          <t>PrieTorres</t>
+        </is>
+      </c>
+      <c r="G46" s="6" t="n">
+        <v>46317</v>
+      </c>
+      <c r="H46" s="5" t="inlineStr">
+        <is>
+          <t>#40, #42, #44, #45, #46, #48, #49, #50, #82</t>
+        </is>
+      </c>
+      <c r="I46" s="5" t="inlineStr">
+        <is>
+          <t>A fazer</t>
+        </is>
+      </c>
+      <c r="J46" s="5" t="inlineStr">
+        <is>
+          <t>Plano da N2</t>
+        </is>
+      </c>
+      <c r="K46" s="5" t="inlineStr">
+        <is>
+          <t>• Seed fora do build: `seedIfEmpty` sai do `main.tsx` e a pasta `lib/seed` deixa de existir
+• `DemoDataControls` fora do build, junto com o uso em `AppLayout.tsx` e o spec `demo-data.cy.ts`
+• Adaptador `localStorage` fora do build: a fábrica só monta repositórios HTTP, e `createLocal*Repository`, `collection.ts` e `createLocalAuthProvider` não são importados por nenhum código de produção
+• Nenhuma referência a `teacher-demo` no código de produção
+• `apps/web/dist` não contém `teacher-demo`, `seeded-at`, `Dados de demonstração`, `demo-sheets` nem `prova-exemplo`
+• App funciona só com banco: sem sessão vai para o login; com o banco vazio, as telas mostram o estado vazio; o que é criado num navegador aparece em outro
+• O tour continua lembrando o que já foi visto (`lib/tour/seen.ts` intacto)
+• Nenhum spec Cypress depende de dado semeado, e a suíte inteira passa
+• `sonar-project.properties` sem `**/seed/**`, com as mesmas exclusões de cobertura do `vite.config.ts`
+• Testes automatizados do caso principal: a fábrica só devolve repositórios HTTP, e um spec Cypress confirma que o menu não tem mais "Dados de demonstração" e que o primeiro acesso mostra o estado vazio
+• Vídeo do teste anexado no PR</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="108" customHeight="1">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>#52</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>chore: republish with backend and cut release 2.0.0</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>Entrega</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>Infraestrutura e API</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>Priscila Torres</t>
+        </is>
+      </c>
+      <c r="F47" s="5" t="inlineStr">
+        <is>
+          <t>PrieTorres</t>
+        </is>
+      </c>
+      <c r="G47" s="6" t="n">
+        <v>46317</v>
+      </c>
+      <c r="H47" s="5" t="inlineStr">
+        <is>
+          <t>#31, #32, #36, #38, #39, #40, #41, #42, #43, #44, #45, #46, #47, #48, #49, #50, #51, #77, #78, #82, #71</t>
+        </is>
+      </c>
+      <c r="I47" s="5" t="inlineStr">
+        <is>
+          <t>A fazer</t>
+        </is>
+      </c>
+      <c r="J47" s="5" t="inlineStr">
+        <is>
+          <t>Plano da N2</t>
+        </is>
+      </c>
+      <c r="K47" s="5" t="inlineStr">
+        <is>
+          <t>• Front publicado apontando para a API: um dado criado num navegador aparece em outro
+• O sistema publicado não mostra "Dados de demonstração" nem aviso de fase simulada, e `GET /health` responde 200
+• Nenhum PR aberto da N2, fora o desta issue
+• Tag e release 2.0.0, criadas pelo workflow "Release do dia" a partir da `main`
+• `package.json` da raiz, de `apps/web` e de `apps/api` em 2.0.0
+• `docs/Versionamento.md` atualizado (manifestos e estado atual)
+• Zip sem `node_modules` nem `.env`, gerado da tag e conferido
+• Evidência (link, print ou vídeo) anexada na issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="134" customHeight="1">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>#55</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>test(e2e): Cypress coverage for access and public lookup against the API</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>Teste automatizado</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>Acesso e consulta pública</t>
+        </is>
+      </c>
+      <c r="E48" s="5" t="inlineStr">
+        <is>
+          <t>Heloísa Fogaça</t>
+        </is>
+      </c>
+      <c r="F48" s="5" t="inlineStr">
+        <is>
+          <t>heloisaFogaca</t>
+        </is>
+      </c>
+      <c r="G48" s="6" t="n">
+        <v>46317</v>
+      </c>
+      <c r="H48" s="5" t="inlineStr">
+        <is>
+          <t>#40, #49, #54, #39</t>
+        </is>
+      </c>
+      <c r="I48" s="5" t="inlineStr">
+        <is>
+          <t>A fazer</t>
+        </is>
+      </c>
+      <c r="J48" s="5" t="inlineStr">
+        <is>
+          <t>Plano da N2</t>
+        </is>
+      </c>
+      <c r="K48" s="5" t="inlineStr">
+        <is>
+          <t>• Specs de login, cadastro, recuperar senha, consulta por QR e privacidade cobrindo fluxo feliz, erro e estado vazio
+• Os quatro estados da consulta pública, o "QR inválido" e o código de PDF regenerado cobertos
+• Redirecionamento sem sessão e bloqueio de login cobertos
+• Cada teste cria os próprios dados pela API, sem depender de dado de demonstração
+• Comando de login reutilizável em `cypress/support/commands.ts`
+• Seletores por nome acessível, nunca por tag ou índice
+• Telas de acesso e a consulta incluídas no `responsive.cy.ts`
+• Suíte inteira verde no CI
+• Testes automatizados do caso principal
+• Vídeo do teste anexado no PR</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="69" customHeight="1">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>#60</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>review: code review of the classes and applications pull requests</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>Code review</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr">
+        <is>
+          <t>Turmas e aplicações</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>Heloísa Fogaça</t>
+        </is>
+      </c>
+      <c r="F49" s="5" t="inlineStr">
+        <is>
+          <t>heloisaFogaca</t>
+        </is>
+      </c>
+      <c r="G49" s="6" t="n">
+        <v>46317</v>
+      </c>
+      <c r="H49" s="5" t="inlineStr">
+        <is>
+          <t>#41, #42, #46, #82</t>
+        </is>
+      </c>
+      <c r="I49" s="5" t="inlineStr">
+        <is>
+          <t>A fazer</t>
+        </is>
+      </c>
+      <c r="J49" s="5" t="inlineStr">
+        <is>
+          <t>Plano da N2</t>
+        </is>
+      </c>
+      <c r="K49" s="5" t="inlineStr">
+        <is>
+          <t>• Revisar e aprovar ou pedir mudanças nos PRs de classes and applications: #41, #42, #46 e #82
+• Conferir em cada PR de API os pontos do passo 2, e os pontos específicos do passo 3
 • Conferir o vídeo do teste contra o checklist da issue
 • Prints das revisões no diário
 • Evidência (link, print ou vídeo) anexada na issue</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="69" customHeight="1">
-      <c r="A42" s="4" t="inlineStr">
-        <is>
-          <t>#59</t>
-        </is>
-      </c>
-      <c r="B42" s="5" t="inlineStr">
-        <is>
-          <t>test(e2e): Cypress coverage for classes and applications against the API</t>
-        </is>
-      </c>
-      <c r="C42" s="5" t="inlineStr">
-        <is>
-          <t>Teste automatizado</t>
-        </is>
-      </c>
-      <c r="D42" s="5" t="inlineStr">
-        <is>
-          <t>Turmas e aplicações</t>
-        </is>
-      </c>
-      <c r="E42" s="5" t="inlineStr">
-        <is>
-          <t>Jeliel Nunes</t>
-        </is>
-      </c>
-      <c r="F42" s="5" t="inlineStr">
-        <is>
-          <t>Jeliell</t>
-        </is>
-      </c>
-      <c r="G42" s="6" t="n">
-        <v>46315</v>
-      </c>
-      <c r="H42" s="5" t="inlineStr">
-        <is>
-          <t>Exploratory test of classes and applications</t>
-        </is>
-      </c>
-      <c r="I42" s="5" t="inlineStr">
+    <row r="50" ht="95" customHeight="1">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>#66</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>qa: exploratory test of grading, dashboard and reports on the real database</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>QA exploratório</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="inlineStr">
+        <is>
+          <t>Correção, painel e relatórios</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="inlineStr">
+        <is>
+          <t>Cleberson Maia</t>
+        </is>
+      </c>
+      <c r="F50" s="5" t="inlineStr">
+        <is>
+          <t>maia202</t>
+        </is>
+      </c>
+      <c r="G50" s="6" t="n">
+        <v>46317</v>
+      </c>
+      <c r="H50" s="5" t="inlineStr">
+        <is>
+          <t>#47, #48, #50, #77, #78</t>
+        </is>
+      </c>
+      <c r="I50" s="5" t="inlineStr">
         <is>
           <t>A fazer</t>
         </is>
       </c>
-      <c r="J42" s="5" t="inlineStr">
+      <c r="J50" s="5" t="inlineStr">
         <is>
           <t>Plano da N2</t>
         </is>
       </c>
-      <c r="K42" s="5" t="inlineStr">
-        <is>
-          <t>• Specs de turmas, alunos, importação, aplicações, PDF cobrindo fluxo feliz, erro e estado vazio
-• Seletores por nome acessível, nunca por tag ou índice
-• Suíte inteira verde no CI
-• Testes automatizados do caso principal
-• Vídeo do teste anexado no PR</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="56" customHeight="1">
-      <c r="A43" s="4" t="inlineStr">
-        <is>
-          <t>#50</t>
-        </is>
-      </c>
-      <c r="B43" s="5" t="inlineStr">
-        <is>
-          <t>feat: dashboard, profile and reports on the API</t>
-        </is>
-      </c>
-      <c r="C43" s="5" t="inlineStr">
-        <is>
-          <t>Desenvolvimento</t>
-        </is>
-      </c>
-      <c r="D43" s="5" t="inlineStr">
-        <is>
-          <t>Correção, painel e relatórios</t>
-        </is>
-      </c>
-      <c r="E43" s="5" t="inlineStr">
-        <is>
-          <t>Fabricio da Silva</t>
-        </is>
-      </c>
-      <c r="F43" s="5" t="inlineStr">
-        <is>
-          <t>fabriciojrr</t>
-        </is>
-      </c>
-      <c r="G43" s="6" t="n">
-        <v>46316</v>
-      </c>
-      <c r="H43" s="5" t="inlineStr">
-        <is>
-          <t>Correction API</t>
-        </is>
-      </c>
-      <c r="I43" s="5" t="inlineStr">
-        <is>
-          <t>A fazer</t>
-        </is>
-      </c>
-      <c r="J43" s="5" t="inlineStr">
-        <is>
-          <t>Plano da N2</t>
-        </is>
-      </c>
-      <c r="K43" s="5" t="inlineStr">
-        <is>
-          <t>• Indicadores e relatórios calculados no servidor
-• Perfil edita dados reais
-• Testes automatizados do caso principal
-• Vídeo do teste anexado no PR</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="56" customHeight="1">
-      <c r="A44" s="4" t="inlineStr">
-        <is>
-          <t>#51</t>
-        </is>
-      </c>
-      <c r="B44" s="5" t="inlineStr">
-        <is>
-          <t>chore(web): remove every simulated data source from production</t>
-        </is>
-      </c>
-      <c r="C44" s="5" t="inlineStr">
-        <is>
-          <t>Desenvolvimento</t>
-        </is>
-      </c>
-      <c r="D44" s="5" t="inlineStr">
-        <is>
-          <t>Infraestrutura e API</t>
-        </is>
-      </c>
-      <c r="E44" s="5" t="inlineStr">
-        <is>
-          <t>Priscila Torres</t>
-        </is>
-      </c>
-      <c r="F44" s="5" t="inlineStr">
-        <is>
-          <t>PrieTorres</t>
-        </is>
-      </c>
-      <c r="G44" s="6" t="n">
-        <v>46316</v>
-      </c>
-      <c r="H44" s="5" t="inlineStr">
-        <is>
-          <t>All screens on the API</t>
-        </is>
-      </c>
-      <c r="I44" s="5" t="inlineStr">
-        <is>
-          <t>A fazer</t>
-        </is>
-      </c>
-      <c r="J44" s="5" t="inlineStr">
-        <is>
-          <t>Plano da N2</t>
-        </is>
-      </c>
-      <c r="K44" s="5" t="inlineStr">
-        <is>
-          <t>• Seed, DemoDataControls e adaptador localStorage fora do build
-• App funciona só com banco
-• Testes automatizados do caso principal
-• Vídeo do teste anexado no PR</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="69" customHeight="1">
-      <c r="A45" s="4" t="inlineStr">
-        <is>
-          <t>#54</t>
-        </is>
-      </c>
-      <c r="B45" s="5" t="inlineStr">
-        <is>
-          <t>qa: exploratory test of access and public lookup on the real database</t>
-        </is>
-      </c>
-      <c r="C45" s="5" t="inlineStr">
-        <is>
-          <t>QA exploratório</t>
-        </is>
-      </c>
-      <c r="D45" s="5" t="inlineStr">
-        <is>
-          <t>Acesso e consulta pública</t>
-        </is>
-      </c>
-      <c r="E45" s="5" t="inlineStr">
-        <is>
-          <t>Fabricio da Silva</t>
-        </is>
-      </c>
-      <c r="F45" s="5" t="inlineStr">
-        <is>
-          <t>fabriciojrr</t>
-        </is>
-      </c>
-      <c r="G45" s="6" t="n">
-        <v>46316</v>
-      </c>
-      <c r="H45" s="5" t="inlineStr">
-        <is>
-          <t>Integração de access and public lookup</t>
-        </is>
-      </c>
-      <c r="I45" s="5" t="inlineStr">
-        <is>
-          <t>A fazer</t>
-        </is>
-      </c>
-      <c r="J45" s="5" t="inlineStr">
-        <is>
-          <t>Plano da N2</t>
-        </is>
-      </c>
-      <c r="K45" s="5" t="inlineStr">
-        <is>
-          <t>• Testar criar/listar/editar/excluir e casos de borda (login, cadastro, recuperar senha, consulta por QR, privacidade)
+      <c r="K50" s="5" t="inlineStr">
+        <is>
+          <t>• Testar criar/listar/editar/excluir e casos de borda (correção, revisão, pendentes, painel, relatórios, perfil), seguindo o roteiro acima
+• Testar com fotos de folhas impressas de verdade e com um arquivo inválido
+• Testar com dois professores: um nunca vê aplicação, correção, imagem ou relatório do outro
 • Abrir uma issue Bug por problema, com vídeo
 • Conferir que nada some ao editar e que não há dado simulado
 • Retestar os bugs corrigidos
@@ -3034,490 +3477,196 @@
         </is>
       </c>
     </row>
-    <row r="46" ht="69" customHeight="1">
-      <c r="A46" s="4" t="inlineStr">
-        <is>
-          <t>#55</t>
-        </is>
-      </c>
-      <c r="B46" s="5" t="inlineStr">
-        <is>
-          <t>test(e2e): Cypress coverage for access and public lookup against the API</t>
-        </is>
-      </c>
-      <c r="C46" s="5" t="inlineStr">
+    <row r="51" ht="95" customHeight="1">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>#67</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>test(e2e): Cypress coverage for grading, dashboard and reports against the API</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
         <is>
           <t>Teste automatizado</t>
         </is>
       </c>
-      <c r="D46" s="5" t="inlineStr">
-        <is>
-          <t>Acesso e consulta pública</t>
-        </is>
-      </c>
-      <c r="E46" s="5" t="inlineStr">
-        <is>
-          <t>Heloísa Fogaça</t>
-        </is>
-      </c>
-      <c r="F46" s="5" t="inlineStr">
-        <is>
-          <t>heloisaFogaca</t>
-        </is>
-      </c>
-      <c r="G46" s="6" t="n">
-        <v>46316</v>
-      </c>
-      <c r="H46" s="5" t="inlineStr">
-        <is>
-          <t>Exploratory test of access and public lookup</t>
-        </is>
-      </c>
-      <c r="I46" s="5" t="inlineStr">
+      <c r="D51" s="5" t="inlineStr">
+        <is>
+          <t>Correção, painel e relatórios</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>Fabricio da Silva</t>
+        </is>
+      </c>
+      <c r="F51" s="5" t="inlineStr">
+        <is>
+          <t>fabriciojrr</t>
+        </is>
+      </c>
+      <c r="G51" s="6" t="n">
+        <v>46317</v>
+      </c>
+      <c r="H51" s="5" t="inlineStr">
+        <is>
+          <t>#66, #47, #48, #50, #77, #39</t>
+        </is>
+      </c>
+      <c r="I51" s="5" t="inlineStr">
         <is>
           <t>A fazer</t>
         </is>
       </c>
-      <c r="J46" s="5" t="inlineStr">
+      <c r="J51" s="5" t="inlineStr">
         <is>
           <t>Plano da N2</t>
         </is>
       </c>
-      <c r="K46" s="5" t="inlineStr">
-        <is>
-          <t>• Specs de login, cadastro, recuperar senha, consulta por QR, privacidade cobrindo fluxo feliz, erro e estado vazio
-• Seletores por nome acessível, nunca por tag ou índice
-• Suíte inteira verde no CI
+      <c r="K51" s="5" t="inlineStr">
+        <is>
+          <t>• Specs de correção, revisão, pendentes, painel, relatórios e perfil cobrindo fluxo feliz, erro e estado vazio, contra a API e o banco
+• Cada spec cria os próprios dados pela API e não depende da ordem de execução
+• Seletores por nome acessível, nunca por tag ou índice, inclusive nos testes que já existem em `grading.cy.ts`
+• Um professor não abre a aplicação, a correção nem o relatório de outro
+• Suíte inteira verde no CI, com a API e o banco de teste no job do Cypress
 • Testes automatizados do caso principal
 • Vídeo do teste anexado no PR</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="69" customHeight="1">
-      <c r="A47" s="4" t="inlineStr">
-        <is>
-          <t>#66</t>
-        </is>
-      </c>
-      <c r="B47" s="5" t="inlineStr">
-        <is>
-          <t>qa: exploratory test of grading, dashboard and reports on the real database</t>
-        </is>
-      </c>
-      <c r="C47" s="5" t="inlineStr">
-        <is>
-          <t>QA exploratório</t>
-        </is>
-      </c>
-      <c r="D47" s="5" t="inlineStr">
+    <row r="52" ht="69" customHeight="1">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>#68</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>review: code review of the grading, dashboard and reports pull requests</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>Code review</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="inlineStr">
         <is>
           <t>Correção, painel e relatórios</t>
         </is>
       </c>
-      <c r="E47" s="5" t="inlineStr">
+      <c r="E52" s="5" t="inlineStr">
         <is>
           <t>Cleberson Maia</t>
         </is>
       </c>
-      <c r="F47" s="5" t="inlineStr">
+      <c r="F52" s="5" t="inlineStr">
         <is>
           <t>maia202</t>
         </is>
       </c>
-      <c r="G47" s="6" t="n">
-        <v>46316</v>
-      </c>
-      <c r="H47" s="5" t="inlineStr">
-        <is>
-          <t>Integração de grading, dashboard and reports</t>
-        </is>
-      </c>
-      <c r="I47" s="5" t="inlineStr">
+      <c r="G52" s="6" t="n">
+        <v>46317</v>
+      </c>
+      <c r="H52" s="5" t="inlineStr">
+        <is>
+          <t>#47, #48, #50, #77, #78</t>
+        </is>
+      </c>
+      <c r="I52" s="5" t="inlineStr">
         <is>
           <t>A fazer</t>
         </is>
       </c>
-      <c r="J47" s="5" t="inlineStr">
+      <c r="J52" s="5" t="inlineStr">
         <is>
           <t>Plano da N2</t>
         </is>
       </c>
-      <c r="K47" s="5" t="inlineStr">
-        <is>
-          <t>• Testar criar/listar/editar/excluir e casos de borda (correção, revisão, pendentes, painel, relatórios, perfil)
-• Abrir uma issue Bug por problema, com vídeo
-• Conferir que nada some ao editar e que não há dado simulado
-• Retestar os bugs corrigidos
-• Evidência (link, print ou vídeo) anexada na issue</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="56" customHeight="1">
-      <c r="A48" s="4" t="inlineStr">
-        <is>
-          <t>#68</t>
-        </is>
-      </c>
-      <c r="B48" s="5" t="inlineStr">
-        <is>
-          <t>review: code review of the grading, dashboard and reports pull requests</t>
-        </is>
-      </c>
-      <c r="C48" s="5" t="inlineStr">
-        <is>
-          <t>Code review</t>
-        </is>
-      </c>
-      <c r="D48" s="5" t="inlineStr">
-        <is>
-          <t>Correção, painel e relatórios</t>
-        </is>
-      </c>
-      <c r="E48" s="5" t="inlineStr">
-        <is>
-          <t>Cleberson Maia</t>
-        </is>
-      </c>
-      <c r="F48" s="5" t="inlineStr">
-        <is>
-          <t>maia202</t>
-        </is>
-      </c>
-      <c r="G48" s="6" t="n">
-        <v>46316</v>
-      </c>
-      <c r="H48" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I48" s="5" t="inlineStr">
-        <is>
-          <t>A fazer</t>
-        </is>
-      </c>
-      <c r="J48" s="5" t="inlineStr">
-        <is>
-          <t>Plano da N2</t>
-        </is>
-      </c>
-      <c r="K48" s="5" t="inlineStr">
-        <is>
-          <t>• Revisar e aprovar ou pedir mudanças nos PRs de grading, dashboard and reports
+      <c r="K52" s="5" t="inlineStr">
+        <is>
+          <t>• Revisar e aprovar ou pedir mudanças nos PRs de grading, dashboard and reports (#47, #48, #50, #77 e #78), com comentário no código e não só aprovação
 • Conferir o vídeo do teste contra o checklist da issue
+• Conferir em cada PR o modelo de dados, o isolamento entre professores e os testes do comportamento novo
 • Prints das revisões no diário
 • Evidência (link, print ou vídeo) anexada na issue</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="95" customHeight="1">
-      <c r="A49" s="4" t="inlineStr">
-        <is>
-          <t>#71</t>
-        </is>
-      </c>
-      <c r="B49" s="5" t="inlineStr">
-        <is>
-          <t>docs: README v2 with integration status</t>
-        </is>
-      </c>
-      <c r="C49" s="5" t="inlineStr">
+    <row r="53" ht="95" customHeight="1">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>#79</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>docs: screen captures with captions in README section 4</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
         <is>
           <t>Documentação</t>
         </is>
       </c>
-      <c r="D49" s="5" t="inlineStr">
+      <c r="D53" s="5" t="inlineStr">
         <is>
           <t>Documentação</t>
         </is>
       </c>
-      <c r="E49" s="5" t="inlineStr">
-        <is>
-          <t>Cleberson Maia</t>
-        </is>
-      </c>
-      <c r="F49" s="5" t="inlineStr">
-        <is>
-          <t>maia202</t>
-        </is>
-      </c>
-      <c r="G49" s="6" t="n">
-        <v>46316</v>
-      </c>
-      <c r="H49" s="5" t="inlineStr">
-        <is>
-          <t>#27, #28, #29, ER diagram</t>
-        </is>
-      </c>
-      <c r="I49" s="5" t="inlineStr">
+      <c r="E53" s="5" t="inlineStr">
+        <is>
+          <t>Jeliel Nunes</t>
+        </is>
+      </c>
+      <c r="F53" s="5" t="inlineStr">
+        <is>
+          <t>Jeliell</t>
+        </is>
+      </c>
+      <c r="G53" s="6" t="n">
+        <v>46317</v>
+      </c>
+      <c r="H53" s="5" t="inlineStr">
+        <is>
+          <t>#40, #42, #44, #45, #46, #48, #49, #50, #51</t>
+        </is>
+      </c>
+      <c r="I53" s="5" t="inlineStr">
         <is>
           <t>A fazer</t>
         </is>
       </c>
-      <c r="J49" s="5" t="inlineStr">
-        <is>
-          <t>Plano da N2</t>
-        </is>
-      </c>
-      <c r="K49" s="5" t="inlineStr">
-        <is>
-          <t>• Tabela do que está ligado ao banco
-• Como rodar API + banco localmente
-• Links para diagramas e DER
-• Evidência (link, print ou vídeo) anexada na issue
-• README na numeração do modelo da disciplina (`modelo_doc.md`), seções 1 a 14
-• Seção 3 (UML) com um parágrafo curto abaixo de cada diagrama
-• Seção 11 com a especificação da API (método, rota e descrição)</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="82" customHeight="1">
-      <c r="A50" s="4" t="inlineStr">
-        <is>
-          <t>#79</t>
-        </is>
-      </c>
-      <c r="B50" s="5" t="inlineStr">
-        <is>
-          <t>docs: screen captures with captions in README section 4</t>
-        </is>
-      </c>
-      <c r="C50" s="5" t="inlineStr">
-        <is>
-          <t>Documentação</t>
-        </is>
-      </c>
-      <c r="D50" s="5" t="inlineStr">
-        <is>
-          <t>Documentação</t>
-        </is>
-      </c>
-      <c r="E50" s="5" t="inlineStr">
-        <is>
-          <t>Jeliel Nunes</t>
-        </is>
-      </c>
-      <c r="F50" s="5" t="inlineStr">
-        <is>
-          <t>Jeliell</t>
-        </is>
-      </c>
-      <c r="G50" s="6" t="n">
-        <v>46316</v>
-      </c>
-      <c r="H50" s="5" t="inlineStr">
-        <is>
-          <t>Telas ligadas à API (#42, #44, #45, #46, #48, #49, #50)</t>
-        </is>
-      </c>
-      <c r="I50" s="5" t="inlineStr">
-        <is>
-          <t>A fazer</t>
-        </is>
-      </c>
-      <c r="J50" s="5" t="inlineStr">
+      <c r="J53" s="5" t="inlineStr">
         <is>
           <t>Feedback da N1</t>
         </is>
       </c>
-      <c r="K50" s="5" t="inlineStr">
+      <c r="K53" s="5" t="inlineStr">
         <is>
           <t>• Um print por tela principal, na ordem do fluxo de navegação (a tela A leva à tela B)
 • Prints tirados da versão hospedada da N2, já com dados do banco
-• Arquivos em `docs/telas/`, com nome em inglês (ex.: `sign-in.png`)
+• Nenhum print com dado de demonstração, botões "Aplicar"/"Limpar" ou dado de aluno real
+• Arquivos em `docs/screens/` (a pasta `docs/telas/` do modelo da disciplina), com nome em inglês (ex.: `sign-in.png`)
 • Legenda de uma linha embaixo de cada print, dizendo o que a tela faz
 • Seção "Telas do Sistema" do README usando os prints
 • Evidência (link, print ou vídeo) anexada na issue</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="82" customHeight="1">
-      <c r="A51" s="4" t="inlineStr">
-        <is>
-          <t>#82</t>
-        </is>
-      </c>
-      <c r="B51" s="5" t="inlineStr">
-        <is>
-          <t>feat: export reports as Excel, CSV and PDF (RF36)</t>
-        </is>
-      </c>
-      <c r="C51" s="5" t="inlineStr">
-        <is>
-          <t>Desenvolvimento</t>
-        </is>
-      </c>
-      <c r="D51" s="5" t="inlineStr">
-        <is>
-          <t>Correção, painel e relatórios</t>
-        </is>
-      </c>
-      <c r="E51" s="5" t="inlineStr">
-        <is>
-          <t>Jeliel Nunes</t>
-        </is>
-      </c>
-      <c r="F51" s="5" t="inlineStr">
-        <is>
-          <t>Jeliell</t>
-        </is>
-      </c>
-      <c r="G51" s="6" t="n">
-        <v>46316</v>
-      </c>
-      <c r="H51" s="5" t="inlineStr">
-        <is>
-          <t>#47, #69</t>
-        </is>
-      </c>
-      <c r="I51" s="5" t="inlineStr">
-        <is>
-          <t>A fazer</t>
-        </is>
-      </c>
-      <c r="J51" s="5" t="inlineStr">
-        <is>
-          <t>Mock da N1 a remover (RF36)</t>
-        </is>
-      </c>
-      <c r="K51" s="5" t="inlineStr">
-        <is>
-          <t>• O botão "Exportar" gera um arquivo de verdade
-• Relatório por aplicação e relatório consolidado exportam em Excel (.xlsx), CSV e PDF (RF36)
-• Uma linha por aluno, com nome, matrícula, versão, nota por questão e total, usando as colunas validadas na #69
-• A exportação roda em segundo plano, sem travar a tela (RF41)
-• Testes automatizados do caso principal
-• Vídeo do teste anexado no PR</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="69" customHeight="1">
-      <c r="A52" s="4" t="inlineStr">
-        <is>
-          <t>#52</t>
-        </is>
-      </c>
-      <c r="B52" s="5" t="inlineStr">
-        <is>
-          <t>chore: republish with backend and cut release 2.0.0</t>
-        </is>
-      </c>
-      <c r="C52" s="5" t="inlineStr">
-        <is>
-          <t>Entrega</t>
-        </is>
-      </c>
-      <c r="D52" s="5" t="inlineStr">
-        <is>
-          <t>Infraestrutura e API</t>
-        </is>
-      </c>
-      <c r="E52" s="5" t="inlineStr">
-        <is>
-          <t>Priscila Torres</t>
-        </is>
-      </c>
-      <c r="F52" s="5" t="inlineStr">
-        <is>
-          <t>PrieTorres</t>
-        </is>
-      </c>
-      <c r="G52" s="6" t="n">
-        <v>46317</v>
-      </c>
-      <c r="H52" s="5" t="inlineStr">
-        <is>
-          <t>Everything above</t>
-        </is>
-      </c>
-      <c r="I52" s="5" t="inlineStr">
-        <is>
-          <t>A fazer</t>
-        </is>
-      </c>
-      <c r="J52" s="5" t="inlineStr">
-        <is>
-          <t>Plano da N2</t>
-        </is>
-      </c>
-      <c r="K52" s="5" t="inlineStr">
-        <is>
-          <t>• Front publicado apontando para a API
-• Nenhum PR aberto da N2
-• Tag e release 2.0.0
-• Zip sem node_modules
-• Evidência (link, print ou vídeo) anexada na issue</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="69" customHeight="1">
-      <c r="A53" s="4" t="inlineStr">
-        <is>
-          <t>#67</t>
-        </is>
-      </c>
-      <c r="B53" s="5" t="inlineStr">
-        <is>
-          <t>test(e2e): Cypress coverage for grading, dashboard and reports against the API</t>
-        </is>
-      </c>
-      <c r="C53" s="5" t="inlineStr">
-        <is>
-          <t>Teste automatizado</t>
-        </is>
-      </c>
-      <c r="D53" s="5" t="inlineStr">
-        <is>
-          <t>Correção, painel e relatórios</t>
-        </is>
-      </c>
-      <c r="E53" s="5" t="inlineStr">
-        <is>
-          <t>Fabricio da Silva</t>
-        </is>
-      </c>
-      <c r="F53" s="5" t="inlineStr">
-        <is>
-          <t>fabriciojrr</t>
-        </is>
-      </c>
-      <c r="G53" s="6" t="n">
-        <v>46317</v>
-      </c>
-      <c r="H53" s="5" t="inlineStr">
-        <is>
-          <t>Exploratory test of grading, dashboard and reports</t>
-        </is>
-      </c>
-      <c r="I53" s="5" t="inlineStr">
-        <is>
-          <t>A fazer</t>
-        </is>
-      </c>
-      <c r="J53" s="5" t="inlineStr">
-        <is>
-          <t>Plano da N2</t>
-        </is>
-      </c>
-      <c r="K53" s="5" t="inlineStr">
-        <is>
-          <t>• Specs de correção, revisão, pendentes, painel, relatórios, perfil cobrindo fluxo feliz, erro e estado vazio
-• Seletores por nome acessível, nunca por tag ou índice
-• Suíte inteira verde no CI
-• Testes automatizados do caso principal
-• Vídeo do teste anexado no PR</t>
-        </is>
-      </c>
-    </row>
     <row r="54" ht="69" customHeight="1">
       <c r="A54" s="4" t="inlineStr">
         <is>
-          <t>#72</t>
+          <t>#80</t>
         </is>
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>docs: N2 logbook — Priscila</t>
+          <t>docs: team roles and contributions in README section 14</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
@@ -3532,12 +3681,12 @@
       </c>
       <c r="E54" s="5" t="inlineStr">
         <is>
-          <t>Priscila Torres</t>
+          <t>Fabricio da Silva</t>
         </is>
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
-          <t>PrieTorres</t>
+          <t>fabriciojrr</t>
         </is>
       </c>
       <c r="G54" s="6" t="n">
@@ -3545,7 +3694,7 @@
       </c>
       <c r="H54" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#71</t>
         </is>
       </c>
       <c r="I54" s="5" t="inlineStr">
@@ -3555,48 +3704,48 @@
       </c>
       <c r="J54" s="5" t="inlineStr">
         <is>
-          <t>Plano da N2</t>
+          <t>Feedback da N1</t>
         </is>
       </c>
       <c r="K54" s="5" t="inlineStr">
         <is>
-          <t>• Separar o que foi feito na N1 e na N2
-• Prints de commits, PRs aprovados/mergeados e reprovações
-• Prints de revisões, bugs e sugestões abertos
-• Comprovação no sistema hospedado
+          <t>• Tabela "Equipe" com o papel e as principais frentes de cada integrante
+• Seção 14 com as contribuições de cada integrante, separando N1 e N2
+• Links para os principais PRs de cada um
+• Texto de cada integrante conferido por ele, com um comentário de cada um no PR
 • Evidência (link, print ou vídeo) anexada na issue</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="69" customHeight="1">
+    <row r="55" ht="82" customHeight="1">
       <c r="A55" s="4" t="inlineStr">
         <is>
-          <t>#73</t>
+          <t>#81</t>
         </is>
       </c>
       <c r="B55" s="5" t="inlineStr">
         <is>
-          <t>docs: N2 logbook — Heloísa</t>
+          <t>review: code review of teammates' pull requests</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>Documentação</t>
+          <t>Code review</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>Documentação</t>
+          <t>Processo e escopo</t>
         </is>
       </c>
       <c r="E55" s="5" t="inlineStr">
         <is>
-          <t>Heloísa Fogaça</t>
+          <t>Priscila Torres</t>
         </is>
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>heloisaFogaca</t>
+          <t>PrieTorres</t>
         </is>
       </c>
       <c r="G55" s="6" t="n">
@@ -3614,305 +3763,10 @@
       </c>
       <c r="J55" s="5" t="inlineStr">
         <is>
-          <t>Plano da N2</t>
+          <t>Feedback da N1</t>
         </is>
       </c>
       <c r="K55" s="5" t="inlineStr">
-        <is>
-          <t>• Separar o que foi feito na N1 e na N2
-• Prints de commits, PRs aprovados/mergeados e reprovações
-• Prints de revisões, bugs e sugestões abertos
-• Comprovação no sistema hospedado
-• Evidência (link, print ou vídeo) anexada na issue</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="69" customHeight="1">
-      <c r="A56" s="4" t="inlineStr">
-        <is>
-          <t>#74</t>
-        </is>
-      </c>
-      <c r="B56" s="5" t="inlineStr">
-        <is>
-          <t>docs: N2 logbook — Jeliel</t>
-        </is>
-      </c>
-      <c r="C56" s="5" t="inlineStr">
-        <is>
-          <t>Documentação</t>
-        </is>
-      </c>
-      <c r="D56" s="5" t="inlineStr">
-        <is>
-          <t>Documentação</t>
-        </is>
-      </c>
-      <c r="E56" s="5" t="inlineStr">
-        <is>
-          <t>Jeliel Nunes</t>
-        </is>
-      </c>
-      <c r="F56" s="5" t="inlineStr">
-        <is>
-          <t>Jeliell</t>
-        </is>
-      </c>
-      <c r="G56" s="6" t="n">
-        <v>46317</v>
-      </c>
-      <c r="H56" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I56" s="5" t="inlineStr">
-        <is>
-          <t>A fazer</t>
-        </is>
-      </c>
-      <c r="J56" s="5" t="inlineStr">
-        <is>
-          <t>Plano da N2</t>
-        </is>
-      </c>
-      <c r="K56" s="5" t="inlineStr">
-        <is>
-          <t>• Separar o que foi feito na N1 e na N2
-• Prints de commits, PRs aprovados/mergeados e reprovações
-• Prints de revisões, bugs e sugestões abertos
-• Comprovação no sistema hospedado
-• Evidência (link, print ou vídeo) anexada na issue</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="69" customHeight="1">
-      <c r="A57" s="4" t="inlineStr">
-        <is>
-          <t>#75</t>
-        </is>
-      </c>
-      <c r="B57" s="5" t="inlineStr">
-        <is>
-          <t>docs: N2 logbook — Cleberson</t>
-        </is>
-      </c>
-      <c r="C57" s="5" t="inlineStr">
-        <is>
-          <t>Documentação</t>
-        </is>
-      </c>
-      <c r="D57" s="5" t="inlineStr">
-        <is>
-          <t>Documentação</t>
-        </is>
-      </c>
-      <c r="E57" s="5" t="inlineStr">
-        <is>
-          <t>Cleberson Maia</t>
-        </is>
-      </c>
-      <c r="F57" s="5" t="inlineStr">
-        <is>
-          <t>maia202</t>
-        </is>
-      </c>
-      <c r="G57" s="6" t="n">
-        <v>46317</v>
-      </c>
-      <c r="H57" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I57" s="5" t="inlineStr">
-        <is>
-          <t>A fazer</t>
-        </is>
-      </c>
-      <c r="J57" s="5" t="inlineStr">
-        <is>
-          <t>Plano da N2</t>
-        </is>
-      </c>
-      <c r="K57" s="5" t="inlineStr">
-        <is>
-          <t>• Separar o que foi feito na N1 e na N2
-• Prints de commits, PRs aprovados/mergeados e reprovações
-• Prints de revisões, bugs e sugestões abertos
-• Comprovação no sistema hospedado
-• Evidência (link, print ou vídeo) anexada na issue</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="69" customHeight="1">
-      <c r="A58" s="4" t="inlineStr">
-        <is>
-          <t>#76</t>
-        </is>
-      </c>
-      <c r="B58" s="5" t="inlineStr">
-        <is>
-          <t>docs: N2 logbook — Fabricio</t>
-        </is>
-      </c>
-      <c r="C58" s="5" t="inlineStr">
-        <is>
-          <t>Documentação</t>
-        </is>
-      </c>
-      <c r="D58" s="5" t="inlineStr">
-        <is>
-          <t>Documentação</t>
-        </is>
-      </c>
-      <c r="E58" s="5" t="inlineStr">
-        <is>
-          <t>Fabricio da Silva</t>
-        </is>
-      </c>
-      <c r="F58" s="5" t="inlineStr">
-        <is>
-          <t>fabriciojrr</t>
-        </is>
-      </c>
-      <c r="G58" s="6" t="n">
-        <v>46317</v>
-      </c>
-      <c r="H58" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I58" s="5" t="inlineStr">
-        <is>
-          <t>A fazer</t>
-        </is>
-      </c>
-      <c r="J58" s="5" t="inlineStr">
-        <is>
-          <t>Plano da N2</t>
-        </is>
-      </c>
-      <c r="K58" s="5" t="inlineStr">
-        <is>
-          <t>• Separar o que foi feito na N1 e na N2
-• Prints de commits, PRs aprovados/mergeados e reprovações
-• Prints de revisões, bugs e sugestões abertos
-• Comprovação no sistema hospedado
-• Evidência (link, print ou vídeo) anexada na issue</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="69" customHeight="1">
-      <c r="A59" s="4" t="inlineStr">
-        <is>
-          <t>#80</t>
-        </is>
-      </c>
-      <c r="B59" s="5" t="inlineStr">
-        <is>
-          <t>docs: team roles and contributions in README section 14</t>
-        </is>
-      </c>
-      <c r="C59" s="5" t="inlineStr">
-        <is>
-          <t>Documentação</t>
-        </is>
-      </c>
-      <c r="D59" s="5" t="inlineStr">
-        <is>
-          <t>Documentação</t>
-        </is>
-      </c>
-      <c r="E59" s="5" t="inlineStr">
-        <is>
-          <t>Fabricio da Silva</t>
-        </is>
-      </c>
-      <c r="F59" s="5" t="inlineStr">
-        <is>
-          <t>fabriciojrr</t>
-        </is>
-      </c>
-      <c r="G59" s="6" t="n">
-        <v>46317</v>
-      </c>
-      <c r="H59" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I59" s="5" t="inlineStr">
-        <is>
-          <t>A fazer</t>
-        </is>
-      </c>
-      <c r="J59" s="5" t="inlineStr">
-        <is>
-          <t>Feedback da N1</t>
-        </is>
-      </c>
-      <c r="K59" s="5" t="inlineStr">
-        <is>
-          <t>• Tabela "Equipe" com o papel e as principais frentes de cada integrante
-• Seção 14 com as contribuições de cada integrante, separando N1 e N2
-• Texto de cada integrante conferido por ele
-• Links para os principais PRs de cada um
-• Evidência (link, print ou vídeo) anexada na issue</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="82" customHeight="1">
-      <c r="A60" s="4" t="inlineStr">
-        <is>
-          <t>#81</t>
-        </is>
-      </c>
-      <c r="B60" s="5" t="inlineStr">
-        <is>
-          <t>review: code review of teammates' pull requests</t>
-        </is>
-      </c>
-      <c r="C60" s="5" t="inlineStr">
-        <is>
-          <t>Code review</t>
-        </is>
-      </c>
-      <c r="D60" s="5" t="inlineStr">
-        <is>
-          <t>Processo e escopo</t>
-        </is>
-      </c>
-      <c r="E60" s="5" t="inlineStr">
-        <is>
-          <t>Priscila Torres</t>
-        </is>
-      </c>
-      <c r="F60" s="5" t="inlineStr">
-        <is>
-          <t>PrieTorres</t>
-        </is>
-      </c>
-      <c r="G60" s="6" t="n">
-        <v>46317</v>
-      </c>
-      <c r="H60" s="5" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I60" s="5" t="inlineStr">
-        <is>
-          <t>A fazer</t>
-        </is>
-      </c>
-      <c r="J60" s="5" t="inlineStr">
-        <is>
-          <t>Feedback da N1</t>
-        </is>
-      </c>
-      <c r="K60" s="5" t="inlineStr">
         <is>
           <t>• PR #23 revisado até 13/10: aprovado e mergeado, ou fechado com o motivo
 • PR #24 revisado até 13/10: aprovado e mergeado, ou fechado com o motivo (está em conflito com a `main`)
@@ -3923,43 +3777,348 @@
         </is>
       </c>
     </row>
-    <row r="61" ht="30" customHeight="1">
+    <row r="56" ht="147" customHeight="1">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>#82</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>feat: export reports as Excel, CSV and PDF (RF36)</t>
+        </is>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>Desenvolvimento</t>
+        </is>
+      </c>
+      <c r="D56" s="5" t="inlineStr">
+        <is>
+          <t>Correção, painel e relatórios</t>
+        </is>
+      </c>
+      <c r="E56" s="5" t="inlineStr">
+        <is>
+          <t>Jeliel Nunes</t>
+        </is>
+      </c>
+      <c r="F56" s="5" t="inlineStr">
+        <is>
+          <t>Jeliell</t>
+        </is>
+      </c>
+      <c r="G56" s="6" t="n">
+        <v>46317</v>
+      </c>
+      <c r="H56" s="5" t="inlineStr">
+        <is>
+          <t>#47, #69, #50</t>
+        </is>
+      </c>
+      <c r="I56" s="5" t="inlineStr">
+        <is>
+          <t>A fazer</t>
+        </is>
+      </c>
+      <c r="J56" s="5" t="inlineStr">
+        <is>
+          <t>Mock da N1 a remover (RF36)</t>
+        </is>
+      </c>
+      <c r="K56" s="5" t="inlineStr">
+        <is>
+          <t>• O botão "Exportar" gera um arquivo de verdade: o `setTimeout` de `ApplicationReportPage.tsx` sai
+• Relatório por aplicação e relatório consolidado exportam em Excel (.xlsx), CSV e PDF (RF36)
+• Uma linha por aluno, com nome, matrícula, versão, nota por questão e total, usando as colunas validadas na #69
+• A nota de cada questão cai na coluna da questão da prova, qualquer que seja a versão do aluno
+• O consolidado sai com uma linha por aplicação, com as mesmas colunas da tela
+• A exportação roda em segundo plano, sem travar a tela (RF41): a tela confirma o início em menos de 1 segundo
+• Quando o arquivo fica pronto, o professor é avisado e baixa o arquivo (RF41)
+• O CSV e o .xlsx abrem no Excel com acentos corretos, e célula começando com `=` não vira fórmula
+• Exportar relatório de aplicação de outro professor responde 404
+• Testes automatizados do caso principal: unitário da montagem das linhas (questão na coluna certa entre versões, folha sem aluno, escape do CSV), supertest das rotas, e Cypress do clique até o download
+• Vídeo do teste anexado no PR</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="82" customHeight="1">
+      <c r="A57" s="4" t="inlineStr">
+        <is>
+          <t>#72</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>docs: N2 logbook — Priscila</t>
+        </is>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>Documentação</t>
+        </is>
+      </c>
+      <c r="D57" s="5" t="inlineStr">
+        <is>
+          <t>Documentação</t>
+        </is>
+      </c>
+      <c r="E57" s="5" t="inlineStr">
+        <is>
+          <t>Priscila Torres</t>
+        </is>
+      </c>
+      <c r="F57" s="5" t="inlineStr">
+        <is>
+          <t>PrieTorres</t>
+        </is>
+      </c>
+      <c r="G57" s="6" t="n">
+        <v>46318</v>
+      </c>
+      <c r="H57" s="5" t="inlineStr">
+        <is>
+          <t>#52</t>
+        </is>
+      </c>
+      <c r="I57" s="5" t="inlineStr">
+        <is>
+          <t>A fazer</t>
+        </is>
+      </c>
+      <c r="J57" s="5" t="inlineStr">
+        <is>
+          <t>Plano da N2</t>
+        </is>
+      </c>
+      <c r="K57" s="5" t="inlineStr">
+        <is>
+          <t>• Separar o que foi feito na N1 e na N2
+• Uma entrada por tarefa da N2, com issue e PR
+• Prints de commits, PRs aprovados/mergeados e reprovações
+• Prints de revisões, bugs e sugestões abertos
+• Comprovação no sistema hospedado
+• Evidência (link, print ou vídeo) anexada na issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="82" customHeight="1">
+      <c r="A58" s="4" t="inlineStr">
+        <is>
+          <t>#73</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="inlineStr">
+        <is>
+          <t>docs: N2 logbook — Heloísa</t>
+        </is>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>Documentação</t>
+        </is>
+      </c>
+      <c r="D58" s="5" t="inlineStr">
+        <is>
+          <t>Documentação</t>
+        </is>
+      </c>
+      <c r="E58" s="5" t="inlineStr">
+        <is>
+          <t>Heloísa Fogaça</t>
+        </is>
+      </c>
+      <c r="F58" s="5" t="inlineStr">
+        <is>
+          <t>heloisaFogaca</t>
+        </is>
+      </c>
+      <c r="G58" s="6" t="n">
+        <v>46318</v>
+      </c>
+      <c r="H58" s="5" t="inlineStr">
+        <is>
+          <t>#52</t>
+        </is>
+      </c>
+      <c r="I58" s="5" t="inlineStr">
+        <is>
+          <t>A fazer</t>
+        </is>
+      </c>
+      <c r="J58" s="5" t="inlineStr">
+        <is>
+          <t>Plano da N2</t>
+        </is>
+      </c>
+      <c r="K58" s="5" t="inlineStr">
+        <is>
+          <t>• Separar o que foi feito na N1 e na N2
+• Uma entrada por tarefa da N2, com issue e PR
+• Prints de commits, PRs aprovados/mergeados e reprovações
+• Prints de revisões, bugs e sugestões abertos
+• Comprovação no sistema hospedado
+• Evidência (link, print ou vídeo) anexada na issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="82" customHeight="1">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>#74</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>docs: N2 logbook — Jeliel</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="inlineStr">
+        <is>
+          <t>Documentação</t>
+        </is>
+      </c>
+      <c r="D59" s="5" t="inlineStr">
+        <is>
+          <t>Documentação</t>
+        </is>
+      </c>
+      <c r="E59" s="5" t="inlineStr">
+        <is>
+          <t>Jeliel Nunes</t>
+        </is>
+      </c>
+      <c r="F59" s="5" t="inlineStr">
+        <is>
+          <t>Jeliell</t>
+        </is>
+      </c>
+      <c r="G59" s="6" t="n">
+        <v>46318</v>
+      </c>
+      <c r="H59" s="5" t="inlineStr">
+        <is>
+          <t>#52</t>
+        </is>
+      </c>
+      <c r="I59" s="5" t="inlineStr">
+        <is>
+          <t>A fazer</t>
+        </is>
+      </c>
+      <c r="J59" s="5" t="inlineStr">
+        <is>
+          <t>Plano da N2</t>
+        </is>
+      </c>
+      <c r="K59" s="5" t="inlineStr">
+        <is>
+          <t>• Separar o que foi feito na N1 e na N2
+• Uma entrada por tarefa da N2, com issue e PR
+• Prints de commits, PRs aprovados/mergeados e reprovações
+• Prints de revisões, bugs e sugestões abertos
+• Comprovação no sistema hospedado
+• Evidência (link, print ou vídeo) anexada na issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="82" customHeight="1">
+      <c r="A60" s="4" t="inlineStr">
+        <is>
+          <t>#75</t>
+        </is>
+      </c>
+      <c r="B60" s="5" t="inlineStr">
+        <is>
+          <t>docs: N2 logbook — Cleberson</t>
+        </is>
+      </c>
+      <c r="C60" s="5" t="inlineStr">
+        <is>
+          <t>Documentação</t>
+        </is>
+      </c>
+      <c r="D60" s="5" t="inlineStr">
+        <is>
+          <t>Documentação</t>
+        </is>
+      </c>
+      <c r="E60" s="5" t="inlineStr">
+        <is>
+          <t>Cleberson Maia</t>
+        </is>
+      </c>
+      <c r="F60" s="5" t="inlineStr">
+        <is>
+          <t>maia202</t>
+        </is>
+      </c>
+      <c r="G60" s="6" t="n">
+        <v>46318</v>
+      </c>
+      <c r="H60" s="5" t="inlineStr">
+        <is>
+          <t>#52</t>
+        </is>
+      </c>
+      <c r="I60" s="5" t="inlineStr">
+        <is>
+          <t>A fazer</t>
+        </is>
+      </c>
+      <c r="J60" s="5" t="inlineStr">
+        <is>
+          <t>Plano da N2</t>
+        </is>
+      </c>
+      <c r="K60" s="5" t="inlineStr">
+        <is>
+          <t>• Separar o que foi feito na N1 e na N2
+• Uma entrada por tarefa da N2, com issue e PR
+• Prints de commits, PRs aprovados/mergeados e reprovações
+• Prints de revisões, bugs e sugestões abertos
+• Comprovação no sistema hospedado
+• Evidência (link, print ou vídeo) anexada na issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="82" customHeight="1">
       <c r="A61" s="4" t="inlineStr">
         <is>
-          <t>#35</t>
+          <t>#76</t>
         </is>
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>Testar passo e cenários da aplicação</t>
+          <t>docs: N2 logbook — Fabricio</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>QA exploratório</t>
+          <t>Documentação</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>Sistema inteiro</t>
+          <t>Documentação</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr">
         <is>
-          <t>Heloísa Fogaça</t>
+          <t>Fabricio da Silva</t>
         </is>
       </c>
       <c r="F61" s="5" t="inlineStr">
         <is>
-          <t>heloisaFogaca</t>
+          <t>fabriciojrr</t>
         </is>
       </c>
       <c r="G61" s="6" t="n">
-        <v>46321</v>
+        <v>46318</v>
       </c>
       <c r="H61" s="5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>#52</t>
         </is>
       </c>
       <c r="I61" s="5" t="inlineStr">
@@ -3969,12 +4128,17 @@
       </c>
       <c r="J61" s="5" t="inlineStr">
         <is>
-          <t>Issue já existente</t>
+          <t>Plano da N2</t>
         </is>
       </c>
       <c r="K61" s="5" t="inlineStr">
         <is>
-          <t>Sem checklist ainda: ver o comentário na issue</t>
+          <t>• Separar o que foi feito na N1 e na N2
+• Uma entrada por tarefa da N2, com issue e PR
+• Prints de commits, PRs aprovados/mergeados e reprovações
+• Prints de revisões, bugs e sugestões abertos
+• Comprovação no sistema hospedado
+• Evidência (link, print ou vídeo) anexada na issue</t>
         </is>
       </c>
     </row>
